--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,184 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7737000</v>
+        <v>7858000</v>
       </c>
       <c r="E8" s="3">
-        <v>11621000</v>
+        <v>7820900</v>
       </c>
       <c r="F8" s="3">
-        <v>8494500</v>
+        <v>11747000</v>
       </c>
       <c r="G8" s="3">
-        <v>8426600</v>
+        <v>8586600</v>
       </c>
       <c r="H8" s="3">
-        <v>9644300</v>
+        <v>8518000</v>
       </c>
       <c r="I8" s="3">
-        <v>10691200</v>
+        <v>9748900</v>
       </c>
       <c r="J8" s="3">
+        <v>10807200</v>
+      </c>
+      <c r="K8" s="3">
         <v>10316900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11487800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14702600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14606000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12587900</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7687800</v>
+        <v>7711900</v>
       </c>
       <c r="E9" s="3">
-        <v>8775400</v>
+        <v>7771200</v>
       </c>
       <c r="F9" s="3">
-        <v>7780800</v>
+        <v>8870600</v>
       </c>
       <c r="G9" s="3">
-        <v>8412300</v>
+        <v>7865100</v>
       </c>
       <c r="H9" s="3">
-        <v>8762200</v>
+        <v>8503600</v>
       </c>
       <c r="I9" s="3">
-        <v>8777600</v>
+        <v>8857200</v>
       </c>
       <c r="J9" s="3">
+        <v>8872800</v>
+      </c>
+      <c r="K9" s="3">
         <v>9235600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10217800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12955200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26827700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25900900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>49100</v>
+        <v>146100</v>
       </c>
       <c r="E10" s="3">
-        <v>2845600</v>
+        <v>49700</v>
       </c>
       <c r="F10" s="3">
-        <v>713700</v>
+        <v>2876400</v>
       </c>
       <c r="G10" s="3">
-        <v>14300</v>
+        <v>721400</v>
       </c>
       <c r="H10" s="3">
-        <v>882200</v>
+        <v>14400</v>
       </c>
       <c r="I10" s="3">
-        <v>1913700</v>
+        <v>891700</v>
       </c>
       <c r="J10" s="3">
+        <v>1934400</v>
+      </c>
+      <c r="K10" s="3">
         <v>1081300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1270000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1747400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-12221700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-13312900</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,47 +861,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>403400</v>
+        <v>419300</v>
       </c>
       <c r="E12" s="3">
-        <v>409700</v>
+        <v>407800</v>
       </c>
       <c r="F12" s="3">
-        <v>322500</v>
+        <v>414200</v>
       </c>
       <c r="G12" s="3">
-        <v>307500</v>
+        <v>326000</v>
       </c>
       <c r="H12" s="3">
-        <v>299300</v>
+        <v>310900</v>
       </c>
       <c r="I12" s="3">
-        <v>308900</v>
+        <v>302500</v>
       </c>
       <c r="J12" s="3">
+        <v>312300</v>
+      </c>
+      <c r="K12" s="3">
         <v>284700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>283900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>329800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>299200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>329400</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,48 +942,54 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>33500</v>
+        <v>40100</v>
       </c>
       <c r="E14" s="3">
-        <v>32800</v>
+        <v>33800</v>
       </c>
       <c r="F14" s="3">
-        <v>12400</v>
+        <v>33200</v>
       </c>
       <c r="G14" s="3">
-        <v>72100</v>
+        <v>12600</v>
       </c>
       <c r="H14" s="3">
-        <v>28300</v>
+        <v>72800</v>
       </c>
       <c r="I14" s="3">
-        <v>51100</v>
+        <v>28600</v>
       </c>
       <c r="J14" s="3">
+        <v>51700</v>
+      </c>
+      <c r="K14" s="3">
         <v>30600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>383500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>82600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>140400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>800400</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,15 +1020,18 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19800</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,86 +1044,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8521900</v>
+        <v>8594000</v>
       </c>
       <c r="E17" s="3">
-        <v>9676400</v>
+        <v>8614300</v>
       </c>
       <c r="F17" s="3">
-        <v>8441600</v>
+        <v>9781300</v>
       </c>
       <c r="G17" s="3">
-        <v>9140400</v>
+        <v>8533100</v>
       </c>
       <c r="H17" s="3">
-        <v>9463600</v>
+        <v>9239500</v>
       </c>
       <c r="I17" s="3">
-        <v>9515400</v>
+        <v>9566200</v>
       </c>
       <c r="J17" s="3">
+        <v>9618600</v>
+      </c>
+      <c r="K17" s="3">
         <v>9960700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11312800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13986800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14455500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14139900</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-784900</v>
+        <v>-736000</v>
       </c>
       <c r="E18" s="3">
-        <v>1944600</v>
+        <v>-793500</v>
       </c>
       <c r="F18" s="3">
-        <v>52900</v>
+        <v>1965700</v>
       </c>
       <c r="G18" s="3">
-        <v>-713700</v>
+        <v>53500</v>
       </c>
       <c r="H18" s="3">
-        <v>180800</v>
+        <v>-721500</v>
       </c>
       <c r="I18" s="3">
-        <v>1175900</v>
+        <v>182700</v>
       </c>
       <c r="J18" s="3">
+        <v>1188600</v>
+      </c>
+      <c r="K18" s="3">
         <v>356200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>175100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>715800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>150500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1552000</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,203 +1146,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>220700</v>
+        <v>135300</v>
       </c>
       <c r="E20" s="3">
-        <v>206800</v>
+        <v>223100</v>
       </c>
       <c r="F20" s="3">
-        <v>126800</v>
+        <v>209000</v>
       </c>
       <c r="G20" s="3">
-        <v>193500</v>
+        <v>128200</v>
       </c>
       <c r="H20" s="3">
-        <v>254300</v>
+        <v>195600</v>
       </c>
       <c r="I20" s="3">
-        <v>148100</v>
+        <v>257100</v>
       </c>
       <c r="J20" s="3">
+        <v>149700</v>
+      </c>
+      <c r="K20" s="3">
         <v>79300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>149800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>149600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>368800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>220500</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>420000</v>
+        <v>432900</v>
       </c>
       <c r="E21" s="3">
-        <v>3204400</v>
+        <v>430300</v>
       </c>
       <c r="F21" s="3">
-        <v>1286900</v>
+        <v>3245200</v>
       </c>
       <c r="G21" s="3">
-        <v>613900</v>
+        <v>1307300</v>
       </c>
       <c r="H21" s="3">
-        <v>1505800</v>
+        <v>627200</v>
       </c>
       <c r="I21" s="3">
-        <v>2463500</v>
+        <v>1528300</v>
       </c>
       <c r="J21" s="3">
+        <v>2496800</v>
+      </c>
+      <c r="K21" s="3">
         <v>1677200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1820300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2908200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2752300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1176800</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>47300</v>
+        <v>86400</v>
       </c>
       <c r="E22" s="3">
-        <v>69500</v>
+        <v>47800</v>
       </c>
       <c r="F22" s="3">
-        <v>92300</v>
+        <v>70300</v>
       </c>
       <c r="G22" s="3">
-        <v>101900</v>
+        <v>93300</v>
       </c>
       <c r="H22" s="3">
-        <v>83500</v>
+        <v>103000</v>
       </c>
       <c r="I22" s="3">
-        <v>89900</v>
+        <v>84400</v>
       </c>
       <c r="J22" s="3">
+        <v>90900</v>
+      </c>
+      <c r="K22" s="3">
         <v>84900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>145700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>335600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>381200</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-611500</v>
+        <v>-687100</v>
       </c>
       <c r="E23" s="3">
-        <v>2081900</v>
+        <v>-618200</v>
       </c>
       <c r="F23" s="3">
-        <v>87400</v>
+        <v>2104400</v>
       </c>
       <c r="G23" s="3">
-        <v>-622100</v>
+        <v>88300</v>
       </c>
       <c r="H23" s="3">
-        <v>351600</v>
+        <v>-628900</v>
       </c>
       <c r="I23" s="3">
-        <v>1234000</v>
+        <v>355400</v>
       </c>
       <c r="J23" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="K23" s="3">
         <v>350700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>242300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>719700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>183700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1712700</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>46000</v>
+        <v>-111900</v>
       </c>
       <c r="E24" s="3">
-        <v>92400</v>
+        <v>46500</v>
       </c>
       <c r="F24" s="3">
+        <v>93400</v>
+      </c>
+      <c r="G24" s="3">
         <v>-3800</v>
       </c>
-      <c r="G24" s="3">
-        <v>55000</v>
-      </c>
       <c r="H24" s="3">
-        <v>102100</v>
+        <v>55600</v>
       </c>
       <c r="I24" s="3">
-        <v>285400</v>
+        <v>103200</v>
       </c>
       <c r="J24" s="3">
+        <v>288500</v>
+      </c>
+      <c r="K24" s="3">
         <v>143600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>116800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>47700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37400</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,87 +1395,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-657500</v>
+        <v>-575200</v>
       </c>
       <c r="E26" s="3">
-        <v>1989400</v>
+        <v>-664600</v>
       </c>
       <c r="F26" s="3">
-        <v>91100</v>
+        <v>2011000</v>
       </c>
       <c r="G26" s="3">
-        <v>-677100</v>
+        <v>92100</v>
       </c>
       <c r="H26" s="3">
-        <v>249500</v>
+        <v>-684500</v>
       </c>
       <c r="I26" s="3">
-        <v>948600</v>
+        <v>252200</v>
       </c>
       <c r="J26" s="3">
+        <v>958900</v>
+      </c>
+      <c r="K26" s="3">
         <v>207100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>154400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>602900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>136000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1750100</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-661500</v>
+        <v>-576900</v>
       </c>
       <c r="E27" s="3">
-        <v>1922700</v>
+        <v>-668700</v>
       </c>
       <c r="F27" s="3">
-        <v>105800</v>
+        <v>1943600</v>
       </c>
       <c r="G27" s="3">
-        <v>-601500</v>
+        <v>107000</v>
       </c>
       <c r="H27" s="3">
-        <v>318500</v>
+        <v>-608000</v>
       </c>
       <c r="I27" s="3">
-        <v>1014500</v>
+        <v>322000</v>
       </c>
       <c r="J27" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="K27" s="3">
         <v>245100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>157200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>589500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>133400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1702400</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,87 +1647,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-220700</v>
+        <v>-135300</v>
       </c>
       <c r="E32" s="3">
-        <v>-206800</v>
+        <v>-223100</v>
       </c>
       <c r="F32" s="3">
-        <v>-126800</v>
+        <v>-209000</v>
       </c>
       <c r="G32" s="3">
-        <v>-193500</v>
+        <v>-128200</v>
       </c>
       <c r="H32" s="3">
-        <v>-254300</v>
+        <v>-195600</v>
       </c>
       <c r="I32" s="3">
-        <v>-148100</v>
+        <v>-257100</v>
       </c>
       <c r="J32" s="3">
+        <v>-149700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-79300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-149800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-149600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-368800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-220500</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-661500</v>
+        <v>-576900</v>
       </c>
       <c r="E33" s="3">
-        <v>1922700</v>
+        <v>-668700</v>
       </c>
       <c r="F33" s="3">
-        <v>105800</v>
+        <v>1943600</v>
       </c>
       <c r="G33" s="3">
-        <v>-601500</v>
+        <v>107000</v>
       </c>
       <c r="H33" s="3">
-        <v>318500</v>
+        <v>-608000</v>
       </c>
       <c r="I33" s="3">
-        <v>1014500</v>
+        <v>322000</v>
       </c>
       <c r="J33" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="K33" s="3">
         <v>245100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>157200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>589500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>133400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1702400</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,92 +1773,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-661500</v>
+        <v>-576900</v>
       </c>
       <c r="E35" s="3">
-        <v>1922700</v>
+        <v>-668700</v>
       </c>
       <c r="F35" s="3">
-        <v>105800</v>
+        <v>1943600</v>
       </c>
       <c r="G35" s="3">
-        <v>-601500</v>
+        <v>107000</v>
       </c>
       <c r="H35" s="3">
-        <v>318500</v>
+        <v>-608000</v>
       </c>
       <c r="I35" s="3">
-        <v>1014500</v>
+        <v>322000</v>
       </c>
       <c r="J35" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="K35" s="3">
         <v>245100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>157200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>589500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>133400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1702400</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,359 +1901,387 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2527200</v>
+        <v>2661000</v>
       </c>
       <c r="E41" s="3">
-        <v>2506300</v>
+        <v>2554600</v>
       </c>
       <c r="F41" s="3">
-        <v>2830100</v>
+        <v>2533400</v>
       </c>
       <c r="G41" s="3">
-        <v>2522100</v>
+        <v>2860800</v>
       </c>
       <c r="H41" s="3">
-        <v>2168300</v>
+        <v>2549500</v>
       </c>
       <c r="I41" s="3">
-        <v>3292400</v>
+        <v>2191800</v>
       </c>
       <c r="J41" s="3">
+        <v>3328100</v>
+      </c>
+      <c r="K41" s="3">
         <v>2514000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2514700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2952400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2677000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2398600</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>144000</v>
+        <v>117700</v>
       </c>
       <c r="E42" s="3">
-        <v>382100</v>
+        <v>145600</v>
       </c>
       <c r="F42" s="3">
-        <v>35100</v>
+        <v>386200</v>
       </c>
       <c r="G42" s="3">
-        <v>118500</v>
+        <v>35500</v>
       </c>
       <c r="H42" s="3">
-        <v>97200</v>
+        <v>119800</v>
       </c>
       <c r="I42" s="3">
-        <v>16200</v>
+        <v>98200</v>
       </c>
       <c r="J42" s="3">
+        <v>16400</v>
+      </c>
+      <c r="K42" s="3">
         <v>17600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>374100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>108900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>238500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>181200</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>624600</v>
+        <v>772200</v>
       </c>
       <c r="E43" s="3">
-        <v>1932900</v>
+        <v>631400</v>
       </c>
       <c r="F43" s="3">
-        <v>1469600</v>
+        <v>1953800</v>
       </c>
       <c r="G43" s="3">
-        <v>1008600</v>
+        <v>1485500</v>
       </c>
       <c r="H43" s="3">
-        <v>1488600</v>
+        <v>1019500</v>
       </c>
       <c r="I43" s="3">
-        <v>1275100</v>
+        <v>1504800</v>
       </c>
       <c r="J43" s="3">
+        <v>1288900</v>
+      </c>
+      <c r="K43" s="3">
         <v>1513900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1111600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2149100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1535600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1418200</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>948800</v>
+        <v>919100</v>
       </c>
       <c r="E44" s="3">
-        <v>1081200</v>
+        <v>959100</v>
       </c>
       <c r="F44" s="3">
-        <v>838700</v>
+        <v>1093000</v>
       </c>
       <c r="G44" s="3">
-        <v>735500</v>
+        <v>847800</v>
       </c>
       <c r="H44" s="3">
-        <v>824800</v>
+        <v>743400</v>
       </c>
       <c r="I44" s="3">
-        <v>779200</v>
+        <v>833700</v>
       </c>
       <c r="J44" s="3">
+        <v>787600</v>
+      </c>
+      <c r="K44" s="3">
         <v>867700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1013600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1311900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1318900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1416400</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>150000</v>
+        <v>100100</v>
       </c>
       <c r="E45" s="3">
-        <v>117600</v>
+        <v>151600</v>
       </c>
       <c r="F45" s="3">
-        <v>103200</v>
+        <v>118900</v>
       </c>
       <c r="G45" s="3">
-        <v>104700</v>
+        <v>104300</v>
       </c>
       <c r="H45" s="3">
-        <v>94400</v>
+        <v>105800</v>
       </c>
       <c r="I45" s="3">
-        <v>285600</v>
+        <v>95400</v>
       </c>
       <c r="J45" s="3">
+        <v>288700</v>
+      </c>
+      <c r="K45" s="3">
         <v>207700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>150200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>163600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>179600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>430500</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4394500</v>
+        <v>4570000</v>
       </c>
       <c r="E46" s="3">
-        <v>6020000</v>
+        <v>4442200</v>
       </c>
       <c r="F46" s="3">
-        <v>5276800</v>
+        <v>6085300</v>
       </c>
       <c r="G46" s="3">
-        <v>4489300</v>
+        <v>5334000</v>
       </c>
       <c r="H46" s="3">
-        <v>4673300</v>
+        <v>4538000</v>
       </c>
       <c r="I46" s="3">
-        <v>5648500</v>
+        <v>4724000</v>
       </c>
       <c r="J46" s="3">
+        <v>5709800</v>
+      </c>
+      <c r="K46" s="3">
         <v>5120900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5164300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6685800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5949700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5845000</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1054800</v>
+        <v>1015200</v>
       </c>
       <c r="E47" s="3">
-        <v>838800</v>
+        <v>1066200</v>
       </c>
       <c r="F47" s="3">
-        <v>629700</v>
+        <v>847900</v>
       </c>
       <c r="G47" s="3">
-        <v>424600</v>
+        <v>636600</v>
       </c>
       <c r="H47" s="3">
-        <v>415900</v>
+        <v>429200</v>
       </c>
       <c r="I47" s="3">
-        <v>311800</v>
+        <v>420400</v>
       </c>
       <c r="J47" s="3">
+        <v>315200</v>
+      </c>
+      <c r="K47" s="3">
         <v>257300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>463800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>535800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>493000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>511800</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5957400</v>
+        <v>5776000</v>
       </c>
       <c r="E48" s="3">
-        <v>5746400</v>
+        <v>6022000</v>
       </c>
       <c r="F48" s="3">
-        <v>6216100</v>
+        <v>5808700</v>
       </c>
       <c r="G48" s="3">
-        <v>6912600</v>
+        <v>6283500</v>
       </c>
       <c r="H48" s="3">
-        <v>6969600</v>
+        <v>6987600</v>
       </c>
       <c r="I48" s="3">
-        <v>7074200</v>
+        <v>7045200</v>
       </c>
       <c r="J48" s="3">
+        <v>7150900</v>
+      </c>
+      <c r="K48" s="3">
         <v>6997600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6670900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8366700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9525100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10554300</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>357300</v>
+        <v>357100</v>
       </c>
       <c r="E49" s="3">
-        <v>368600</v>
+        <v>361100</v>
       </c>
       <c r="F49" s="3">
-        <v>401300</v>
+        <v>372600</v>
       </c>
       <c r="G49" s="3">
-        <v>401500</v>
+        <v>405700</v>
       </c>
       <c r="H49" s="3">
-        <v>419400</v>
+        <v>405900</v>
       </c>
       <c r="I49" s="3">
-        <v>412900</v>
+        <v>423900</v>
       </c>
       <c r="J49" s="3">
+        <v>417400</v>
+      </c>
+      <c r="K49" s="3">
         <v>426400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>464700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>140000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>155500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>496700</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,48 +2360,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>363500</v>
+        <v>433900</v>
       </c>
       <c r="E52" s="3">
-        <v>344000</v>
+        <v>367500</v>
       </c>
       <c r="F52" s="3">
-        <v>244000</v>
+        <v>347800</v>
       </c>
       <c r="G52" s="3">
-        <v>237900</v>
+        <v>246700</v>
       </c>
       <c r="H52" s="3">
-        <v>370100</v>
+        <v>240400</v>
       </c>
       <c r="I52" s="3">
-        <v>392100</v>
+        <v>374100</v>
       </c>
       <c r="J52" s="3">
+        <v>396400</v>
+      </c>
+      <c r="K52" s="3">
         <v>671000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>802900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>204900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>183100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>546100</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12127500</v>
+        <v>12152200</v>
       </c>
       <c r="E54" s="3">
-        <v>13317800</v>
+        <v>12259000</v>
       </c>
       <c r="F54" s="3">
-        <v>12767900</v>
+        <v>13462300</v>
       </c>
       <c r="G54" s="3">
-        <v>12465900</v>
+        <v>12906400</v>
       </c>
       <c r="H54" s="3">
-        <v>12848200</v>
+        <v>12601100</v>
       </c>
       <c r="I54" s="3">
-        <v>13839500</v>
+        <v>12987600</v>
       </c>
       <c r="J54" s="3">
+        <v>13989600</v>
+      </c>
+      <c r="K54" s="3">
         <v>13473300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13566700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15933200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16306400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17953800</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,242 +2525,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1485000</v>
+        <v>1541300</v>
       </c>
       <c r="E57" s="3">
-        <v>1987600</v>
+        <v>1501100</v>
       </c>
       <c r="F57" s="3">
-        <v>1718300</v>
+        <v>2009100</v>
       </c>
       <c r="G57" s="3">
-        <v>1606900</v>
+        <v>1737000</v>
       </c>
       <c r="H57" s="3">
-        <v>1837800</v>
+        <v>1624400</v>
       </c>
       <c r="I57" s="3">
-        <v>1710200</v>
+        <v>1857700</v>
       </c>
       <c r="J57" s="3">
+        <v>1728800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1880100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1957900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2695200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2749000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2711000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>457600</v>
+        <v>347600</v>
       </c>
       <c r="E58" s="3">
-        <v>545900</v>
+        <v>462600</v>
       </c>
       <c r="F58" s="3">
-        <v>549400</v>
+        <v>551800</v>
       </c>
       <c r="G58" s="3">
-        <v>374400</v>
+        <v>555400</v>
       </c>
       <c r="H58" s="3">
-        <v>945000</v>
+        <v>378500</v>
       </c>
       <c r="I58" s="3">
-        <v>363000</v>
+        <v>955200</v>
       </c>
       <c r="J58" s="3">
+        <v>367000</v>
+      </c>
+      <c r="K58" s="3">
         <v>583200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1297600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2053100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2323000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1799700</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1103600</v>
+        <v>1108200</v>
       </c>
       <c r="E59" s="3">
-        <v>1346200</v>
+        <v>1115600</v>
       </c>
       <c r="F59" s="3">
-        <v>815200</v>
+        <v>1360800</v>
       </c>
       <c r="G59" s="3">
-        <v>856700</v>
+        <v>824000</v>
       </c>
       <c r="H59" s="3">
-        <v>1259500</v>
+        <v>866000</v>
       </c>
       <c r="I59" s="3">
-        <v>1288600</v>
+        <v>1273100</v>
       </c>
       <c r="J59" s="3">
+        <v>1302600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1213000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1250800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1524400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1289400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1861700</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3046200</v>
+        <v>2997100</v>
       </c>
       <c r="E60" s="3">
-        <v>3879700</v>
+        <v>3079300</v>
       </c>
       <c r="F60" s="3">
-        <v>3082900</v>
+        <v>3921800</v>
       </c>
       <c r="G60" s="3">
-        <v>2838100</v>
+        <v>3116300</v>
       </c>
       <c r="H60" s="3">
-        <v>4042200</v>
+        <v>2868800</v>
       </c>
       <c r="I60" s="3">
-        <v>3361900</v>
+        <v>4086000</v>
       </c>
       <c r="J60" s="3">
+        <v>3398300</v>
+      </c>
+      <c r="K60" s="3">
         <v>3676300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4506200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6272600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6361400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6372400</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2557900</v>
+        <v>3492500</v>
       </c>
       <c r="E61" s="3">
-        <v>1473800</v>
+        <v>2585700</v>
       </c>
       <c r="F61" s="3">
-        <v>3434900</v>
+        <v>1489800</v>
       </c>
       <c r="G61" s="3">
-        <v>3537600</v>
+        <v>3472200</v>
       </c>
       <c r="H61" s="3">
-        <v>1777800</v>
+        <v>3576000</v>
       </c>
       <c r="I61" s="3">
-        <v>3211900</v>
+        <v>1797100</v>
       </c>
       <c r="J61" s="3">
+        <v>3246700</v>
+      </c>
+      <c r="K61" s="3">
         <v>3329000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2185000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3086500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4157200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5657500</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>522600</v>
+        <v>422400</v>
       </c>
       <c r="E62" s="3">
-        <v>504100</v>
+        <v>528300</v>
       </c>
       <c r="F62" s="3">
-        <v>174700</v>
+        <v>509500</v>
       </c>
       <c r="G62" s="3">
-        <v>197200</v>
+        <v>176600</v>
       </c>
       <c r="H62" s="3">
-        <v>216500</v>
+        <v>199400</v>
       </c>
       <c r="I62" s="3">
-        <v>204300</v>
+        <v>218800</v>
       </c>
       <c r="J62" s="3">
+        <v>206500</v>
+      </c>
+      <c r="K62" s="3">
         <v>209400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>351700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>307100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>421000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>494700</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,48 +2900,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6324600</v>
+        <v>7108200</v>
       </c>
       <c r="E66" s="3">
-        <v>6051300</v>
+        <v>6393200</v>
       </c>
       <c r="F66" s="3">
-        <v>7037000</v>
+        <v>6116900</v>
       </c>
       <c r="G66" s="3">
-        <v>6927300</v>
+        <v>7113300</v>
       </c>
       <c r="H66" s="3">
-        <v>6488500</v>
+        <v>7002400</v>
       </c>
       <c r="I66" s="3">
-        <v>7313900</v>
+        <v>6558800</v>
       </c>
       <c r="J66" s="3">
+        <v>7393200</v>
+      </c>
+      <c r="K66" s="3">
         <v>7791200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7765000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10362500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11431900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12993100</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,48 +3128,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1570000</v>
+        <v>1010900</v>
       </c>
       <c r="E72" s="3">
-        <v>2529000</v>
+        <v>1587000</v>
       </c>
       <c r="F72" s="3">
-        <v>948600</v>
+        <v>2556400</v>
       </c>
       <c r="G72" s="3">
-        <v>718000</v>
+        <v>958900</v>
       </c>
       <c r="H72" s="3">
-        <v>1468600</v>
+        <v>725800</v>
       </c>
       <c r="I72" s="3">
-        <v>1602500</v>
+        <v>1484500</v>
       </c>
       <c r="J72" s="3">
+        <v>1619900</v>
+      </c>
+      <c r="K72" s="3">
         <v>760000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>650600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-239800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-768200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1816500</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,48 +3296,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5802900</v>
+        <v>5044000</v>
       </c>
       <c r="E76" s="3">
-        <v>7266500</v>
+        <v>5865800</v>
       </c>
       <c r="F76" s="3">
-        <v>5730900</v>
+        <v>7345300</v>
       </c>
       <c r="G76" s="3">
-        <v>5538700</v>
+        <v>5793100</v>
       </c>
       <c r="H76" s="3">
-        <v>6359700</v>
+        <v>5598700</v>
       </c>
       <c r="I76" s="3">
-        <v>6525600</v>
+        <v>6428700</v>
       </c>
       <c r="J76" s="3">
+        <v>6596400</v>
+      </c>
+      <c r="K76" s="3">
         <v>5682000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5801700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5570800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4874500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4960800</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,92 +3380,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-661500</v>
+        <v>-576900</v>
       </c>
       <c r="E81" s="3">
-        <v>1922700</v>
+        <v>-668700</v>
       </c>
       <c r="F81" s="3">
-        <v>105800</v>
+        <v>1943600</v>
       </c>
       <c r="G81" s="3">
-        <v>-601500</v>
+        <v>107000</v>
       </c>
       <c r="H81" s="3">
-        <v>318500</v>
+        <v>-608000</v>
       </c>
       <c r="I81" s="3">
-        <v>1014500</v>
+        <v>322000</v>
       </c>
       <c r="J81" s="3">
+        <v>1025500</v>
+      </c>
+      <c r="K81" s="3">
         <v>245100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>157200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>589500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>133400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1702400</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,47 +3490,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>986500</v>
+        <v>1030100</v>
       </c>
       <c r="E83" s="3">
-        <v>1055400</v>
+        <v>997200</v>
       </c>
       <c r="F83" s="3">
-        <v>1109700</v>
+        <v>1066800</v>
       </c>
       <c r="G83" s="3">
-        <v>1136700</v>
+        <v>1121700</v>
       </c>
       <c r="H83" s="3">
-        <v>1073000</v>
+        <v>1149000</v>
       </c>
       <c r="I83" s="3">
-        <v>1142100</v>
+        <v>1084700</v>
       </c>
       <c r="J83" s="3">
+        <v>1154500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1244400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1522100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2049600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2232400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2503700</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,48 +3739,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>845500</v>
+        <v>316700</v>
       </c>
       <c r="E89" s="3">
-        <v>3283000</v>
+        <v>854700</v>
       </c>
       <c r="F89" s="3">
-        <v>807200</v>
+        <v>3318600</v>
       </c>
       <c r="G89" s="3">
-        <v>649900</v>
+        <v>815900</v>
       </c>
       <c r="H89" s="3">
-        <v>1260300</v>
+        <v>657000</v>
       </c>
       <c r="I89" s="3">
-        <v>2644800</v>
+        <v>1274000</v>
       </c>
       <c r="J89" s="3">
+        <v>2673500</v>
+      </c>
+      <c r="K89" s="3">
         <v>1150400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1976700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2283400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1741500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1189000</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,47 +3802,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1127000</v>
+        <v>-848900</v>
       </c>
       <c r="E91" s="3">
-        <v>-534100</v>
+        <v>-1139300</v>
       </c>
       <c r="F91" s="3">
-        <v>-489100</v>
+        <v>-539900</v>
       </c>
       <c r="G91" s="3">
-        <v>-926300</v>
+        <v>-494400</v>
       </c>
       <c r="H91" s="3">
-        <v>-1090000</v>
+        <v>-936300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1375700</v>
+        <v>-1101900</v>
       </c>
       <c r="J91" s="3">
+        <v>-1390600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1449000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1066100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-611300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-893100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1441200</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,48 +3925,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1000500</v>
+        <v>-762300</v>
       </c>
       <c r="E94" s="3">
-        <v>-951500</v>
+        <v>-1011300</v>
       </c>
       <c r="F94" s="3">
-        <v>-555200</v>
+        <v>-961800</v>
       </c>
       <c r="G94" s="3">
-        <v>-881300</v>
+        <v>-561200</v>
       </c>
       <c r="H94" s="3">
-        <v>-1081500</v>
+        <v>-890900</v>
       </c>
       <c r="I94" s="3">
-        <v>-1369000</v>
+        <v>-1093200</v>
       </c>
       <c r="J94" s="3">
+        <v>-1383800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1325100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1011700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-472100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-814700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1436200</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,47 +3988,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-300200</v>
+        <v>-194400</v>
       </c>
       <c r="E96" s="3">
-        <v>-89400</v>
+        <v>-303500</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-90300</v>
       </c>
       <c r="G96" s="3">
-        <v>-150900</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-452600</v>
+        <v>-152500</v>
       </c>
       <c r="I96" s="3">
-        <v>-169000</v>
+        <v>-457500</v>
       </c>
       <c r="J96" s="3">
+        <v>-170800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-105600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-153400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-52000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,124 +4153,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>73800</v>
+        <v>582000</v>
       </c>
       <c r="E100" s="3">
-        <v>-2616800</v>
+        <v>74600</v>
       </c>
       <c r="F100" s="3">
-        <v>84800</v>
+        <v>-2645200</v>
       </c>
       <c r="G100" s="3">
-        <v>650300</v>
+        <v>85700</v>
       </c>
       <c r="H100" s="3">
-        <v>-1311900</v>
+        <v>657300</v>
       </c>
       <c r="I100" s="3">
-        <v>-420400</v>
+        <v>-1326100</v>
       </c>
       <c r="J100" s="3">
+        <v>-425000</v>
+      </c>
+      <c r="K100" s="3">
         <v>336100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1092800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1622400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-939600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-197600</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>102100</v>
+        <v>-30100</v>
       </c>
       <c r="E101" s="3">
-        <v>-38600</v>
+        <v>103200</v>
       </c>
       <c r="F101" s="3">
-        <v>-28800</v>
+        <v>-39000</v>
       </c>
       <c r="G101" s="3">
-        <v>-65000</v>
+        <v>-29100</v>
       </c>
       <c r="H101" s="3">
-        <v>9000</v>
+        <v>-65700</v>
       </c>
       <c r="I101" s="3">
-        <v>-77000</v>
+        <v>9100</v>
       </c>
       <c r="J101" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-120400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>29400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>21000</v>
+        <v>106400</v>
       </c>
       <c r="E102" s="3">
-        <v>-323800</v>
+        <v>21200</v>
       </c>
       <c r="F102" s="3">
-        <v>308000</v>
+        <v>-327400</v>
       </c>
       <c r="G102" s="3">
-        <v>353800</v>
+        <v>311400</v>
       </c>
       <c r="H102" s="3">
-        <v>-1124100</v>
+        <v>357700</v>
       </c>
       <c r="I102" s="3">
-        <v>778400</v>
+        <v>-1136300</v>
       </c>
       <c r="J102" s="3">
+        <v>786800</v>
+      </c>
+      <c r="K102" s="3">
         <v>41100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-98300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>203600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-445600</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7858000</v>
+        <v>7689400</v>
       </c>
       <c r="E8" s="3">
-        <v>7820900</v>
+        <v>7653000</v>
       </c>
       <c r="F8" s="3">
-        <v>11747000</v>
+        <v>11494900</v>
       </c>
       <c r="G8" s="3">
-        <v>8586600</v>
+        <v>8402300</v>
       </c>
       <c r="H8" s="3">
-        <v>8518000</v>
+        <v>8335200</v>
       </c>
       <c r="I8" s="3">
-        <v>9748900</v>
+        <v>9539700</v>
       </c>
       <c r="J8" s="3">
-        <v>10807200</v>
+        <v>10575300</v>
       </c>
       <c r="K8" s="3">
         <v>10316900</v>
@@ -766,25 +766,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7711900</v>
+        <v>7546400</v>
       </c>
       <c r="E9" s="3">
-        <v>7771200</v>
+        <v>7604400</v>
       </c>
       <c r="F9" s="3">
-        <v>8870600</v>
+        <v>8680200</v>
       </c>
       <c r="G9" s="3">
-        <v>7865100</v>
+        <v>7696400</v>
       </c>
       <c r="H9" s="3">
-        <v>8503600</v>
+        <v>8321100</v>
       </c>
       <c r="I9" s="3">
-        <v>8857200</v>
+        <v>8667100</v>
       </c>
       <c r="J9" s="3">
-        <v>8872800</v>
+        <v>8682400</v>
       </c>
       <c r="K9" s="3">
         <v>9235600</v>
@@ -808,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>146100</v>
+        <v>143000</v>
       </c>
       <c r="E10" s="3">
-        <v>49700</v>
+        <v>48600</v>
       </c>
       <c r="F10" s="3">
-        <v>2876400</v>
+        <v>2814700</v>
       </c>
       <c r="G10" s="3">
-        <v>721400</v>
+        <v>706000</v>
       </c>
       <c r="H10" s="3">
-        <v>14400</v>
+        <v>14100</v>
       </c>
       <c r="I10" s="3">
-        <v>891700</v>
+        <v>872600</v>
       </c>
       <c r="J10" s="3">
-        <v>1934400</v>
+        <v>1892900</v>
       </c>
       <c r="K10" s="3">
         <v>1081300</v>
@@ -868,25 +868,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>419300</v>
+        <v>410300</v>
       </c>
       <c r="E12" s="3">
-        <v>407800</v>
+        <v>399000</v>
       </c>
       <c r="F12" s="3">
-        <v>414200</v>
+        <v>405300</v>
       </c>
       <c r="G12" s="3">
-        <v>326000</v>
+        <v>319000</v>
       </c>
       <c r="H12" s="3">
-        <v>310900</v>
+        <v>304200</v>
       </c>
       <c r="I12" s="3">
-        <v>302500</v>
+        <v>296000</v>
       </c>
       <c r="J12" s="3">
-        <v>312300</v>
+        <v>305600</v>
       </c>
       <c r="K12" s="3">
         <v>284700</v>
@@ -952,25 +952,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>40100</v>
+        <v>39200</v>
       </c>
       <c r="E14" s="3">
-        <v>33800</v>
+        <v>33100</v>
       </c>
       <c r="F14" s="3">
-        <v>33200</v>
+        <v>32500</v>
       </c>
       <c r="G14" s="3">
-        <v>12600</v>
+        <v>12300</v>
       </c>
       <c r="H14" s="3">
-        <v>72800</v>
+        <v>71300</v>
       </c>
       <c r="I14" s="3">
-        <v>28600</v>
+        <v>27900</v>
       </c>
       <c r="J14" s="3">
-        <v>51700</v>
+        <v>50600</v>
       </c>
       <c r="K14" s="3">
         <v>30600</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8594000</v>
+        <v>8409600</v>
       </c>
       <c r="E17" s="3">
-        <v>8614300</v>
+        <v>8429500</v>
       </c>
       <c r="F17" s="3">
-        <v>9781300</v>
+        <v>9571400</v>
       </c>
       <c r="G17" s="3">
-        <v>8533100</v>
+        <v>8350000</v>
       </c>
       <c r="H17" s="3">
-        <v>9239500</v>
+        <v>9041200</v>
       </c>
       <c r="I17" s="3">
-        <v>9566200</v>
+        <v>9360900</v>
       </c>
       <c r="J17" s="3">
-        <v>9618600</v>
+        <v>9412200</v>
       </c>
       <c r="K17" s="3">
         <v>9960700</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-736000</v>
+        <v>-720200</v>
       </c>
       <c r="E18" s="3">
-        <v>-793500</v>
+        <v>-776400</v>
       </c>
       <c r="F18" s="3">
-        <v>1965700</v>
+        <v>1923500</v>
       </c>
       <c r="G18" s="3">
-        <v>53500</v>
+        <v>52300</v>
       </c>
       <c r="H18" s="3">
-        <v>-721500</v>
+        <v>-706000</v>
       </c>
       <c r="I18" s="3">
-        <v>182700</v>
+        <v>178800</v>
       </c>
       <c r="J18" s="3">
-        <v>1188600</v>
+        <v>1163100</v>
       </c>
       <c r="K18" s="3">
         <v>356200</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>135300</v>
+        <v>132400</v>
       </c>
       <c r="E20" s="3">
-        <v>223100</v>
+        <v>218300</v>
       </c>
       <c r="F20" s="3">
-        <v>209000</v>
+        <v>204500</v>
       </c>
       <c r="G20" s="3">
-        <v>128200</v>
+        <v>125400</v>
       </c>
       <c r="H20" s="3">
-        <v>195600</v>
+        <v>191400</v>
       </c>
       <c r="I20" s="3">
-        <v>257100</v>
+        <v>251600</v>
       </c>
       <c r="J20" s="3">
-        <v>149700</v>
+        <v>146500</v>
       </c>
       <c r="K20" s="3">
         <v>79300</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>432900</v>
+        <v>416600</v>
       </c>
       <c r="E21" s="3">
-        <v>430300</v>
+        <v>414200</v>
       </c>
       <c r="F21" s="3">
-        <v>3245200</v>
+        <v>3168300</v>
       </c>
       <c r="G21" s="3">
-        <v>1307300</v>
+        <v>1271500</v>
       </c>
       <c r="H21" s="3">
-        <v>627200</v>
+        <v>605800</v>
       </c>
       <c r="I21" s="3">
-        <v>1528300</v>
+        <v>1488000</v>
       </c>
       <c r="J21" s="3">
-        <v>2496800</v>
+        <v>2435300</v>
       </c>
       <c r="K21" s="3">
         <v>1677200</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>86400</v>
+        <v>84500</v>
       </c>
       <c r="E22" s="3">
-        <v>47800</v>
+        <v>46800</v>
       </c>
       <c r="F22" s="3">
-        <v>70300</v>
+        <v>68800</v>
       </c>
       <c r="G22" s="3">
-        <v>93300</v>
+        <v>91300</v>
       </c>
       <c r="H22" s="3">
-        <v>103000</v>
+        <v>100800</v>
       </c>
       <c r="I22" s="3">
-        <v>84400</v>
+        <v>82600</v>
       </c>
       <c r="J22" s="3">
-        <v>90900</v>
+        <v>88900</v>
       </c>
       <c r="K22" s="3">
         <v>84900</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-687100</v>
+        <v>-672400</v>
       </c>
       <c r="E23" s="3">
-        <v>-618200</v>
+        <v>-604900</v>
       </c>
       <c r="F23" s="3">
-        <v>2104400</v>
+        <v>2059300</v>
       </c>
       <c r="G23" s="3">
-        <v>88300</v>
+        <v>86400</v>
       </c>
       <c r="H23" s="3">
-        <v>-628900</v>
+        <v>-615400</v>
       </c>
       <c r="I23" s="3">
-        <v>355400</v>
+        <v>347800</v>
       </c>
       <c r="J23" s="3">
-        <v>1247400</v>
+        <v>1220700</v>
       </c>
       <c r="K23" s="3">
         <v>350700</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-111900</v>
+        <v>-109500</v>
       </c>
       <c r="E24" s="3">
-        <v>46500</v>
+        <v>45500</v>
       </c>
       <c r="F24" s="3">
-        <v>93400</v>
+        <v>91400</v>
       </c>
       <c r="G24" s="3">
-        <v>-3800</v>
+        <v>-3700</v>
       </c>
       <c r="H24" s="3">
-        <v>55600</v>
+        <v>54400</v>
       </c>
       <c r="I24" s="3">
-        <v>103200</v>
+        <v>101000</v>
       </c>
       <c r="J24" s="3">
-        <v>288500</v>
+        <v>282300</v>
       </c>
       <c r="K24" s="3">
         <v>143600</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-575200</v>
+        <v>-562900</v>
       </c>
       <c r="E26" s="3">
-        <v>-664600</v>
+        <v>-650400</v>
       </c>
       <c r="F26" s="3">
-        <v>2011000</v>
+        <v>1967900</v>
       </c>
       <c r="G26" s="3">
-        <v>92100</v>
+        <v>90200</v>
       </c>
       <c r="H26" s="3">
-        <v>-684500</v>
+        <v>-669800</v>
       </c>
       <c r="I26" s="3">
-        <v>252200</v>
+        <v>246800</v>
       </c>
       <c r="J26" s="3">
-        <v>958900</v>
+        <v>938300</v>
       </c>
       <c r="K26" s="3">
         <v>207100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-576900</v>
+        <v>-564500</v>
       </c>
       <c r="E27" s="3">
-        <v>-668700</v>
+        <v>-654400</v>
       </c>
       <c r="F27" s="3">
-        <v>1943600</v>
+        <v>1901900</v>
       </c>
       <c r="G27" s="3">
-        <v>107000</v>
+        <v>104700</v>
       </c>
       <c r="H27" s="3">
-        <v>-608000</v>
+        <v>-594900</v>
       </c>
       <c r="I27" s="3">
-        <v>322000</v>
+        <v>315100</v>
       </c>
       <c r="J27" s="3">
-        <v>1025500</v>
+        <v>1003500</v>
       </c>
       <c r="K27" s="3">
         <v>245100</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-135300</v>
+        <v>-132400</v>
       </c>
       <c r="E32" s="3">
-        <v>-223100</v>
+        <v>-218300</v>
       </c>
       <c r="F32" s="3">
-        <v>-209000</v>
+        <v>-204500</v>
       </c>
       <c r="G32" s="3">
-        <v>-128200</v>
+        <v>-125400</v>
       </c>
       <c r="H32" s="3">
-        <v>-195600</v>
+        <v>-191400</v>
       </c>
       <c r="I32" s="3">
-        <v>-257100</v>
+        <v>-251600</v>
       </c>
       <c r="J32" s="3">
-        <v>-149700</v>
+        <v>-146500</v>
       </c>
       <c r="K32" s="3">
         <v>-79300</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-576900</v>
+        <v>-564500</v>
       </c>
       <c r="E33" s="3">
-        <v>-668700</v>
+        <v>-654400</v>
       </c>
       <c r="F33" s="3">
-        <v>1943600</v>
+        <v>1901900</v>
       </c>
       <c r="G33" s="3">
-        <v>107000</v>
+        <v>104700</v>
       </c>
       <c r="H33" s="3">
-        <v>-608000</v>
+        <v>-594900</v>
       </c>
       <c r="I33" s="3">
-        <v>322000</v>
+        <v>315100</v>
       </c>
       <c r="J33" s="3">
-        <v>1025500</v>
+        <v>1003500</v>
       </c>
       <c r="K33" s="3">
         <v>245100</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-576900</v>
+        <v>-564500</v>
       </c>
       <c r="E35" s="3">
-        <v>-668700</v>
+        <v>-654400</v>
       </c>
       <c r="F35" s="3">
-        <v>1943600</v>
+        <v>1901900</v>
       </c>
       <c r="G35" s="3">
-        <v>107000</v>
+        <v>104700</v>
       </c>
       <c r="H35" s="3">
-        <v>-608000</v>
+        <v>-594900</v>
       </c>
       <c r="I35" s="3">
-        <v>322000</v>
+        <v>315100</v>
       </c>
       <c r="J35" s="3">
-        <v>1025500</v>
+        <v>1003500</v>
       </c>
       <c r="K35" s="3">
         <v>245100</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2661000</v>
+        <v>2603900</v>
       </c>
       <c r="E41" s="3">
-        <v>2554600</v>
+        <v>2499800</v>
       </c>
       <c r="F41" s="3">
-        <v>2533400</v>
+        <v>2479100</v>
       </c>
       <c r="G41" s="3">
-        <v>2860800</v>
+        <v>2799400</v>
       </c>
       <c r="H41" s="3">
-        <v>2549500</v>
+        <v>2494700</v>
       </c>
       <c r="I41" s="3">
-        <v>2191800</v>
+        <v>2144800</v>
       </c>
       <c r="J41" s="3">
-        <v>3328100</v>
+        <v>3256700</v>
       </c>
       <c r="K41" s="3">
         <v>2514000</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>117700</v>
+        <v>115200</v>
       </c>
       <c r="E42" s="3">
-        <v>145600</v>
+        <v>142400</v>
       </c>
       <c r="F42" s="3">
-        <v>386200</v>
+        <v>377900</v>
       </c>
       <c r="G42" s="3">
-        <v>35500</v>
+        <v>34700</v>
       </c>
       <c r="H42" s="3">
-        <v>119800</v>
+        <v>117200</v>
       </c>
       <c r="I42" s="3">
-        <v>98200</v>
+        <v>96100</v>
       </c>
       <c r="J42" s="3">
-        <v>16400</v>
+        <v>16100</v>
       </c>
       <c r="K42" s="3">
         <v>17600</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>772200</v>
+        <v>755600</v>
       </c>
       <c r="E43" s="3">
-        <v>631400</v>
+        <v>617800</v>
       </c>
       <c r="F43" s="3">
-        <v>1953800</v>
+        <v>1911900</v>
       </c>
       <c r="G43" s="3">
-        <v>1485500</v>
+        <v>1453700</v>
       </c>
       <c r="H43" s="3">
-        <v>1019500</v>
+        <v>997600</v>
       </c>
       <c r="I43" s="3">
-        <v>1504800</v>
+        <v>1472500</v>
       </c>
       <c r="J43" s="3">
-        <v>1288900</v>
+        <v>1261300</v>
       </c>
       <c r="K43" s="3">
         <v>1513900</v>
@@ -2034,25 +2034,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>919100</v>
+        <v>899400</v>
       </c>
       <c r="E44" s="3">
-        <v>959100</v>
+        <v>938500</v>
       </c>
       <c r="F44" s="3">
-        <v>1093000</v>
+        <v>1069500</v>
       </c>
       <c r="G44" s="3">
-        <v>847800</v>
+        <v>829600</v>
       </c>
       <c r="H44" s="3">
-        <v>743400</v>
+        <v>727500</v>
       </c>
       <c r="I44" s="3">
-        <v>833700</v>
+        <v>815800</v>
       </c>
       <c r="J44" s="3">
-        <v>787600</v>
+        <v>770700</v>
       </c>
       <c r="K44" s="3">
         <v>867700</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100100</v>
+        <v>97900</v>
       </c>
       <c r="E45" s="3">
-        <v>151600</v>
+        <v>148300</v>
       </c>
       <c r="F45" s="3">
-        <v>118900</v>
+        <v>116300</v>
       </c>
       <c r="G45" s="3">
-        <v>104300</v>
+        <v>102100</v>
       </c>
       <c r="H45" s="3">
-        <v>105800</v>
+        <v>103500</v>
       </c>
       <c r="I45" s="3">
-        <v>95400</v>
+        <v>93400</v>
       </c>
       <c r="J45" s="3">
-        <v>288700</v>
+        <v>282500</v>
       </c>
       <c r="K45" s="3">
         <v>207700</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4570000</v>
+        <v>4472000</v>
       </c>
       <c r="E46" s="3">
-        <v>4442200</v>
+        <v>4346900</v>
       </c>
       <c r="F46" s="3">
-        <v>6085300</v>
+        <v>5954700</v>
       </c>
       <c r="G46" s="3">
-        <v>5334000</v>
+        <v>5219500</v>
       </c>
       <c r="H46" s="3">
-        <v>4538000</v>
+        <v>4440600</v>
       </c>
       <c r="I46" s="3">
-        <v>4724000</v>
+        <v>4622600</v>
       </c>
       <c r="J46" s="3">
-        <v>5709800</v>
+        <v>5587200</v>
       </c>
       <c r="K46" s="3">
         <v>5120900</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1015200</v>
+        <v>993400</v>
       </c>
       <c r="E47" s="3">
-        <v>1066200</v>
+        <v>1043300</v>
       </c>
       <c r="F47" s="3">
-        <v>847900</v>
+        <v>829700</v>
       </c>
       <c r="G47" s="3">
-        <v>636600</v>
+        <v>622900</v>
       </c>
       <c r="H47" s="3">
-        <v>429200</v>
+        <v>420000</v>
       </c>
       <c r="I47" s="3">
-        <v>420400</v>
+        <v>411400</v>
       </c>
       <c r="J47" s="3">
-        <v>315200</v>
+        <v>308400</v>
       </c>
       <c r="K47" s="3">
         <v>257300</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5776000</v>
+        <v>5652000</v>
       </c>
       <c r="E48" s="3">
-        <v>6022000</v>
+        <v>5892800</v>
       </c>
       <c r="F48" s="3">
-        <v>5808700</v>
+        <v>5684100</v>
       </c>
       <c r="G48" s="3">
-        <v>6283500</v>
+        <v>6148700</v>
       </c>
       <c r="H48" s="3">
-        <v>6987600</v>
+        <v>6837600</v>
       </c>
       <c r="I48" s="3">
-        <v>7045200</v>
+        <v>6894000</v>
       </c>
       <c r="J48" s="3">
-        <v>7150900</v>
+        <v>6997400</v>
       </c>
       <c r="K48" s="3">
         <v>6997600</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>357100</v>
+        <v>349400</v>
       </c>
       <c r="E49" s="3">
-        <v>361100</v>
+        <v>353400</v>
       </c>
       <c r="F49" s="3">
-        <v>372600</v>
+        <v>364600</v>
       </c>
       <c r="G49" s="3">
-        <v>405700</v>
+        <v>397000</v>
       </c>
       <c r="H49" s="3">
-        <v>405900</v>
+        <v>397200</v>
       </c>
       <c r="I49" s="3">
-        <v>423900</v>
+        <v>414800</v>
       </c>
       <c r="J49" s="3">
-        <v>417400</v>
+        <v>408400</v>
       </c>
       <c r="K49" s="3">
         <v>426400</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>433900</v>
+        <v>424600</v>
       </c>
       <c r="E52" s="3">
-        <v>367500</v>
+        <v>359600</v>
       </c>
       <c r="F52" s="3">
-        <v>347800</v>
+        <v>340300</v>
       </c>
       <c r="G52" s="3">
-        <v>246700</v>
+        <v>241400</v>
       </c>
       <c r="H52" s="3">
-        <v>240400</v>
+        <v>235300</v>
       </c>
       <c r="I52" s="3">
-        <v>374100</v>
+        <v>366100</v>
       </c>
       <c r="J52" s="3">
-        <v>396400</v>
+        <v>387900</v>
       </c>
       <c r="K52" s="3">
         <v>671000</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12152200</v>
+        <v>11891400</v>
       </c>
       <c r="E54" s="3">
-        <v>12259000</v>
+        <v>11995900</v>
       </c>
       <c r="F54" s="3">
-        <v>13462300</v>
+        <v>13173400</v>
       </c>
       <c r="G54" s="3">
-        <v>12906400</v>
+        <v>12629500</v>
       </c>
       <c r="H54" s="3">
-        <v>12601100</v>
+        <v>12330700</v>
       </c>
       <c r="I54" s="3">
-        <v>12987600</v>
+        <v>12708900</v>
       </c>
       <c r="J54" s="3">
-        <v>13989600</v>
+        <v>13689400</v>
       </c>
       <c r="K54" s="3">
         <v>13473300</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1541300</v>
+        <v>1508200</v>
       </c>
       <c r="E57" s="3">
-        <v>1501100</v>
+        <v>1468900</v>
       </c>
       <c r="F57" s="3">
-        <v>2009100</v>
+        <v>1966000</v>
       </c>
       <c r="G57" s="3">
-        <v>1737000</v>
+        <v>1699700</v>
       </c>
       <c r="H57" s="3">
-        <v>1624400</v>
+        <v>1589500</v>
       </c>
       <c r="I57" s="3">
-        <v>1857700</v>
+        <v>1817800</v>
       </c>
       <c r="J57" s="3">
-        <v>1728800</v>
+        <v>1691700</v>
       </c>
       <c r="K57" s="3">
         <v>1880100</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>347600</v>
+        <v>340200</v>
       </c>
       <c r="E58" s="3">
-        <v>462600</v>
+        <v>452600</v>
       </c>
       <c r="F58" s="3">
-        <v>551800</v>
+        <v>540000</v>
       </c>
       <c r="G58" s="3">
-        <v>555400</v>
+        <v>543400</v>
       </c>
       <c r="H58" s="3">
-        <v>378500</v>
+        <v>370400</v>
       </c>
       <c r="I58" s="3">
-        <v>955200</v>
+        <v>934700</v>
       </c>
       <c r="J58" s="3">
-        <v>367000</v>
+        <v>359100</v>
       </c>
       <c r="K58" s="3">
         <v>583200</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1108200</v>
+        <v>1084400</v>
       </c>
       <c r="E59" s="3">
-        <v>1115600</v>
+        <v>1091600</v>
       </c>
       <c r="F59" s="3">
-        <v>1360800</v>
+        <v>1331600</v>
       </c>
       <c r="G59" s="3">
-        <v>824000</v>
+        <v>806300</v>
       </c>
       <c r="H59" s="3">
-        <v>866000</v>
+        <v>847400</v>
       </c>
       <c r="I59" s="3">
-        <v>1273100</v>
+        <v>1245800</v>
       </c>
       <c r="J59" s="3">
-        <v>1302600</v>
+        <v>1274600</v>
       </c>
       <c r="K59" s="3">
         <v>1213000</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2997100</v>
+        <v>2932800</v>
       </c>
       <c r="E60" s="3">
-        <v>3079300</v>
+        <v>3013200</v>
       </c>
       <c r="F60" s="3">
-        <v>3921800</v>
+        <v>3837600</v>
       </c>
       <c r="G60" s="3">
-        <v>3116300</v>
+        <v>3049500</v>
       </c>
       <c r="H60" s="3">
-        <v>2868800</v>
+        <v>2807300</v>
       </c>
       <c r="I60" s="3">
-        <v>4086000</v>
+        <v>3998400</v>
       </c>
       <c r="J60" s="3">
-        <v>3398300</v>
+        <v>3325400</v>
       </c>
       <c r="K60" s="3">
         <v>3676300</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3492500</v>
+        <v>3417600</v>
       </c>
       <c r="E61" s="3">
-        <v>2585700</v>
+        <v>2530200</v>
       </c>
       <c r="F61" s="3">
-        <v>1489800</v>
+        <v>1457800</v>
       </c>
       <c r="G61" s="3">
-        <v>3472200</v>
+        <v>3397700</v>
       </c>
       <c r="H61" s="3">
-        <v>3576000</v>
+        <v>3499200</v>
       </c>
       <c r="I61" s="3">
-        <v>1797100</v>
+        <v>1758600</v>
       </c>
       <c r="J61" s="3">
-        <v>3246700</v>
+        <v>3177100</v>
       </c>
       <c r="K61" s="3">
         <v>3329000</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>422400</v>
+        <v>413300</v>
       </c>
       <c r="E62" s="3">
-        <v>528300</v>
+        <v>516900</v>
       </c>
       <c r="F62" s="3">
-        <v>509500</v>
+        <v>498600</v>
       </c>
       <c r="G62" s="3">
-        <v>176600</v>
+        <v>172900</v>
       </c>
       <c r="H62" s="3">
-        <v>199400</v>
+        <v>195100</v>
       </c>
       <c r="I62" s="3">
-        <v>218800</v>
+        <v>214100</v>
       </c>
       <c r="J62" s="3">
-        <v>206500</v>
+        <v>202100</v>
       </c>
       <c r="K62" s="3">
         <v>209400</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7108200</v>
+        <v>6955700</v>
       </c>
       <c r="E66" s="3">
-        <v>6393200</v>
+        <v>6256000</v>
       </c>
       <c r="F66" s="3">
-        <v>6116900</v>
+        <v>5985700</v>
       </c>
       <c r="G66" s="3">
-        <v>7113300</v>
+        <v>6960700</v>
       </c>
       <c r="H66" s="3">
-        <v>7002400</v>
+        <v>6852100</v>
       </c>
       <c r="I66" s="3">
-        <v>6558800</v>
+        <v>6418100</v>
       </c>
       <c r="J66" s="3">
-        <v>7393200</v>
+        <v>7234500</v>
       </c>
       <c r="K66" s="3">
         <v>7791200</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1010900</v>
+        <v>989200</v>
       </c>
       <c r="E72" s="3">
-        <v>1587000</v>
+        <v>1552900</v>
       </c>
       <c r="F72" s="3">
-        <v>2556400</v>
+        <v>2501600</v>
       </c>
       <c r="G72" s="3">
-        <v>958900</v>
+        <v>938300</v>
       </c>
       <c r="H72" s="3">
-        <v>725800</v>
+        <v>710200</v>
       </c>
       <c r="I72" s="3">
-        <v>1484500</v>
+        <v>1452700</v>
       </c>
       <c r="J72" s="3">
-        <v>1619900</v>
+        <v>1585100</v>
       </c>
       <c r="K72" s="3">
         <v>760000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5044000</v>
+        <v>4935800</v>
       </c>
       <c r="E76" s="3">
-        <v>5865800</v>
+        <v>5739900</v>
       </c>
       <c r="F76" s="3">
-        <v>7345300</v>
+        <v>7187700</v>
       </c>
       <c r="G76" s="3">
-        <v>5793100</v>
+        <v>5668800</v>
       </c>
       <c r="H76" s="3">
-        <v>5598700</v>
+        <v>5478600</v>
       </c>
       <c r="I76" s="3">
-        <v>6428700</v>
+        <v>6290800</v>
       </c>
       <c r="J76" s="3">
-        <v>6596400</v>
+        <v>6454900</v>
       </c>
       <c r="K76" s="3">
         <v>5682000</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-576900</v>
+        <v>-564500</v>
       </c>
       <c r="E81" s="3">
-        <v>-668700</v>
+        <v>-654400</v>
       </c>
       <c r="F81" s="3">
-        <v>1943600</v>
+        <v>1901900</v>
       </c>
       <c r="G81" s="3">
-        <v>107000</v>
+        <v>104700</v>
       </c>
       <c r="H81" s="3">
-        <v>-608000</v>
+        <v>-594900</v>
       </c>
       <c r="I81" s="3">
-        <v>322000</v>
+        <v>315100</v>
       </c>
       <c r="J81" s="3">
-        <v>1025500</v>
+        <v>1003500</v>
       </c>
       <c r="K81" s="3">
         <v>245100</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1030100</v>
+        <v>1008000</v>
       </c>
       <c r="E83" s="3">
-        <v>997200</v>
+        <v>975800</v>
       </c>
       <c r="F83" s="3">
-        <v>1066800</v>
+        <v>1043900</v>
       </c>
       <c r="G83" s="3">
-        <v>1121700</v>
+        <v>1097700</v>
       </c>
       <c r="H83" s="3">
-        <v>1149000</v>
+        <v>1124400</v>
       </c>
       <c r="I83" s="3">
-        <v>1084700</v>
+        <v>1061400</v>
       </c>
       <c r="J83" s="3">
-        <v>1154500</v>
+        <v>1129700</v>
       </c>
       <c r="K83" s="3">
         <v>1244400</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>316700</v>
+        <v>309900</v>
       </c>
       <c r="E89" s="3">
-        <v>854700</v>
+        <v>836400</v>
       </c>
       <c r="F89" s="3">
-        <v>3318600</v>
+        <v>3247400</v>
       </c>
       <c r="G89" s="3">
-        <v>815900</v>
+        <v>798400</v>
       </c>
       <c r="H89" s="3">
-        <v>657000</v>
+        <v>642900</v>
       </c>
       <c r="I89" s="3">
-        <v>1274000</v>
+        <v>1246600</v>
       </c>
       <c r="J89" s="3">
-        <v>2673500</v>
+        <v>2616100</v>
       </c>
       <c r="K89" s="3">
         <v>1150400</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-848900</v>
+        <v>-830700</v>
       </c>
       <c r="E91" s="3">
-        <v>-1139300</v>
+        <v>-1114800</v>
       </c>
       <c r="F91" s="3">
-        <v>-539900</v>
+        <v>-528300</v>
       </c>
       <c r="G91" s="3">
-        <v>-494400</v>
+        <v>-483800</v>
       </c>
       <c r="H91" s="3">
-        <v>-936300</v>
+        <v>-916200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1101900</v>
+        <v>-1078200</v>
       </c>
       <c r="J91" s="3">
-        <v>-1390600</v>
+        <v>-1360800</v>
       </c>
       <c r="K91" s="3">
         <v>-1449000</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-762300</v>
+        <v>-745900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1011300</v>
+        <v>-989600</v>
       </c>
       <c r="F94" s="3">
-        <v>-961800</v>
+        <v>-941200</v>
       </c>
       <c r="G94" s="3">
-        <v>-561200</v>
+        <v>-549100</v>
       </c>
       <c r="H94" s="3">
-        <v>-890900</v>
+        <v>-871800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1093200</v>
+        <v>-1069800</v>
       </c>
       <c r="J94" s="3">
-        <v>-1383800</v>
+        <v>-1354100</v>
       </c>
       <c r="K94" s="3">
         <v>-1325100</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-194400</v>
+        <v>-190200</v>
       </c>
       <c r="E96" s="3">
-        <v>-303500</v>
+        <v>-296900</v>
       </c>
       <c r="F96" s="3">
-        <v>-90300</v>
+        <v>-88400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-152500</v>
+        <v>-149200</v>
       </c>
       <c r="I96" s="3">
-        <v>-457500</v>
+        <v>-447700</v>
       </c>
       <c r="J96" s="3">
-        <v>-170800</v>
+        <v>-167100</v>
       </c>
       <c r="K96" s="3">
         <v>-105600</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>582000</v>
+        <v>569500</v>
       </c>
       <c r="E100" s="3">
-        <v>74600</v>
+        <v>73000</v>
       </c>
       <c r="F100" s="3">
-        <v>-2645200</v>
+        <v>-2588400</v>
       </c>
       <c r="G100" s="3">
-        <v>85700</v>
+        <v>83800</v>
       </c>
       <c r="H100" s="3">
-        <v>657300</v>
+        <v>643200</v>
       </c>
       <c r="I100" s="3">
-        <v>-1326100</v>
+        <v>-1297700</v>
       </c>
       <c r="J100" s="3">
-        <v>-425000</v>
+        <v>-415900</v>
       </c>
       <c r="K100" s="3">
         <v>336100</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-30100</v>
+        <v>-29400</v>
       </c>
       <c r="E101" s="3">
-        <v>103200</v>
+        <v>101000</v>
       </c>
       <c r="F101" s="3">
-        <v>-39000</v>
+        <v>-38200</v>
       </c>
       <c r="G101" s="3">
-        <v>-29100</v>
+        <v>-28500</v>
       </c>
       <c r="H101" s="3">
-        <v>-65700</v>
+        <v>-64300</v>
       </c>
       <c r="I101" s="3">
-        <v>9100</v>
+        <v>8900</v>
       </c>
       <c r="J101" s="3">
-        <v>-77800</v>
+        <v>-76200</v>
       </c>
       <c r="K101" s="3">
         <v>-120400</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>106400</v>
+        <v>104100</v>
       </c>
       <c r="E102" s="3">
-        <v>21200</v>
+        <v>20700</v>
       </c>
       <c r="F102" s="3">
-        <v>-327400</v>
+        <v>-320300</v>
       </c>
       <c r="G102" s="3">
-        <v>311400</v>
+        <v>304700</v>
       </c>
       <c r="H102" s="3">
-        <v>357700</v>
+        <v>350000</v>
       </c>
       <c r="I102" s="3">
-        <v>-1136300</v>
+        <v>-1111900</v>
       </c>
       <c r="J102" s="3">
-        <v>786800</v>
+        <v>770000</v>
       </c>
       <c r="K102" s="3">
         <v>41100</v>

--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7689400</v>
+        <v>7763800</v>
       </c>
       <c r="E8" s="3">
-        <v>7653000</v>
+        <v>7727100</v>
       </c>
       <c r="F8" s="3">
-        <v>11494900</v>
+        <v>11606200</v>
       </c>
       <c r="G8" s="3">
-        <v>8402300</v>
+        <v>8483600</v>
       </c>
       <c r="H8" s="3">
-        <v>8335200</v>
+        <v>8415900</v>
       </c>
       <c r="I8" s="3">
-        <v>9539700</v>
+        <v>9632000</v>
       </c>
       <c r="J8" s="3">
-        <v>10575300</v>
+        <v>10677600</v>
       </c>
       <c r="K8" s="3">
         <v>10316900</v>
@@ -766,25 +766,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7546400</v>
+        <v>7619400</v>
       </c>
       <c r="E9" s="3">
-        <v>7604400</v>
+        <v>7678000</v>
       </c>
       <c r="F9" s="3">
-        <v>8680200</v>
+        <v>8764200</v>
       </c>
       <c r="G9" s="3">
-        <v>7696400</v>
+        <v>7770800</v>
       </c>
       <c r="H9" s="3">
-        <v>8321100</v>
+        <v>8401600</v>
       </c>
       <c r="I9" s="3">
-        <v>8667100</v>
+        <v>8751000</v>
       </c>
       <c r="J9" s="3">
-        <v>8682400</v>
+        <v>8766400</v>
       </c>
       <c r="K9" s="3">
         <v>9235600</v>
@@ -808,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>143000</v>
+        <v>144400</v>
       </c>
       <c r="E10" s="3">
-        <v>48600</v>
+        <v>49100</v>
       </c>
       <c r="F10" s="3">
-        <v>2814700</v>
+        <v>2841900</v>
       </c>
       <c r="G10" s="3">
-        <v>706000</v>
+        <v>712800</v>
       </c>
       <c r="H10" s="3">
-        <v>14100</v>
+        <v>14300</v>
       </c>
       <c r="I10" s="3">
-        <v>872600</v>
+        <v>881000</v>
       </c>
       <c r="J10" s="3">
-        <v>1892900</v>
+        <v>1911200</v>
       </c>
       <c r="K10" s="3">
         <v>1081300</v>
@@ -868,25 +868,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>410300</v>
+        <v>414300</v>
       </c>
       <c r="E12" s="3">
-        <v>399000</v>
+        <v>402900</v>
       </c>
       <c r="F12" s="3">
-        <v>405300</v>
+        <v>409200</v>
       </c>
       <c r="G12" s="3">
-        <v>319000</v>
+        <v>322100</v>
       </c>
       <c r="H12" s="3">
-        <v>304200</v>
+        <v>307100</v>
       </c>
       <c r="I12" s="3">
-        <v>296000</v>
+        <v>298900</v>
       </c>
       <c r="J12" s="3">
-        <v>305600</v>
+        <v>308600</v>
       </c>
       <c r="K12" s="3">
         <v>284700</v>
@@ -952,25 +952,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>39200</v>
+        <v>39600</v>
       </c>
       <c r="E14" s="3">
-        <v>33100</v>
+        <v>33400</v>
       </c>
       <c r="F14" s="3">
-        <v>32500</v>
+        <v>32800</v>
       </c>
       <c r="G14" s="3">
-        <v>12300</v>
+        <v>12400</v>
       </c>
       <c r="H14" s="3">
-        <v>71300</v>
+        <v>72000</v>
       </c>
       <c r="I14" s="3">
-        <v>27900</v>
+        <v>28200</v>
       </c>
       <c r="J14" s="3">
-        <v>50600</v>
+        <v>51100</v>
       </c>
       <c r="K14" s="3">
         <v>30600</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8409600</v>
+        <v>8491000</v>
       </c>
       <c r="E17" s="3">
-        <v>8429500</v>
+        <v>8511000</v>
       </c>
       <c r="F17" s="3">
-        <v>9571400</v>
+        <v>9664000</v>
       </c>
       <c r="G17" s="3">
-        <v>8350000</v>
+        <v>8430800</v>
       </c>
       <c r="H17" s="3">
-        <v>9041200</v>
+        <v>9128700</v>
       </c>
       <c r="I17" s="3">
-        <v>9360900</v>
+        <v>9451500</v>
       </c>
       <c r="J17" s="3">
-        <v>9412200</v>
+        <v>9503200</v>
       </c>
       <c r="K17" s="3">
         <v>9960700</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-720200</v>
+        <v>-727200</v>
       </c>
       <c r="E18" s="3">
-        <v>-776400</v>
+        <v>-783900</v>
       </c>
       <c r="F18" s="3">
-        <v>1923500</v>
+        <v>1942100</v>
       </c>
       <c r="G18" s="3">
-        <v>52300</v>
+        <v>52800</v>
       </c>
       <c r="H18" s="3">
-        <v>-706000</v>
+        <v>-712800</v>
       </c>
       <c r="I18" s="3">
-        <v>178800</v>
+        <v>180600</v>
       </c>
       <c r="J18" s="3">
-        <v>1163100</v>
+        <v>1174400</v>
       </c>
       <c r="K18" s="3">
         <v>356200</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>132400</v>
+        <v>133700</v>
       </c>
       <c r="E20" s="3">
-        <v>218300</v>
+        <v>220400</v>
       </c>
       <c r="F20" s="3">
-        <v>204500</v>
+        <v>206500</v>
       </c>
       <c r="G20" s="3">
-        <v>125400</v>
+        <v>126600</v>
       </c>
       <c r="H20" s="3">
-        <v>191400</v>
+        <v>193300</v>
       </c>
       <c r="I20" s="3">
-        <v>251600</v>
+        <v>254000</v>
       </c>
       <c r="J20" s="3">
-        <v>146500</v>
+        <v>147900</v>
       </c>
       <c r="K20" s="3">
         <v>79300</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>416600</v>
+        <v>420300</v>
       </c>
       <c r="E21" s="3">
-        <v>414200</v>
+        <v>417900</v>
       </c>
       <c r="F21" s="3">
-        <v>3168300</v>
+        <v>3198600</v>
       </c>
       <c r="G21" s="3">
-        <v>1271500</v>
+        <v>1283500</v>
       </c>
       <c r="H21" s="3">
-        <v>605800</v>
+        <v>611300</v>
       </c>
       <c r="I21" s="3">
-        <v>1488000</v>
+        <v>1502100</v>
       </c>
       <c r="J21" s="3">
-        <v>2435300</v>
+        <v>2458500</v>
       </c>
       <c r="K21" s="3">
         <v>1677200</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>84500</v>
+        <v>85300</v>
       </c>
       <c r="E22" s="3">
-        <v>46800</v>
+        <v>47200</v>
       </c>
       <c r="F22" s="3">
-        <v>68800</v>
+        <v>69400</v>
       </c>
       <c r="G22" s="3">
-        <v>91300</v>
+        <v>92200</v>
       </c>
       <c r="H22" s="3">
-        <v>100800</v>
+        <v>101800</v>
       </c>
       <c r="I22" s="3">
-        <v>82600</v>
+        <v>83400</v>
       </c>
       <c r="J22" s="3">
-        <v>88900</v>
+        <v>89800</v>
       </c>
       <c r="K22" s="3">
         <v>84900</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-672400</v>
+        <v>-678900</v>
       </c>
       <c r="E23" s="3">
-        <v>-604900</v>
+        <v>-610700</v>
       </c>
       <c r="F23" s="3">
-        <v>2059300</v>
+        <v>2079200</v>
       </c>
       <c r="G23" s="3">
-        <v>86400</v>
+        <v>87300</v>
       </c>
       <c r="H23" s="3">
-        <v>-615400</v>
+        <v>-621300</v>
       </c>
       <c r="I23" s="3">
-        <v>347800</v>
+        <v>351200</v>
       </c>
       <c r="J23" s="3">
-        <v>1220700</v>
+        <v>1232500</v>
       </c>
       <c r="K23" s="3">
         <v>350700</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-109500</v>
+        <v>-110600</v>
       </c>
       <c r="E24" s="3">
-        <v>45500</v>
+        <v>45900</v>
       </c>
       <c r="F24" s="3">
-        <v>91400</v>
+        <v>92300</v>
       </c>
       <c r="G24" s="3">
         <v>-3700</v>
       </c>
       <c r="H24" s="3">
-        <v>54400</v>
+        <v>54900</v>
       </c>
       <c r="I24" s="3">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="J24" s="3">
-        <v>282300</v>
+        <v>285100</v>
       </c>
       <c r="K24" s="3">
         <v>143600</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-562900</v>
+        <v>-568300</v>
       </c>
       <c r="E26" s="3">
-        <v>-650400</v>
+        <v>-656700</v>
       </c>
       <c r="F26" s="3">
-        <v>1967900</v>
+        <v>1986900</v>
       </c>
       <c r="G26" s="3">
-        <v>90200</v>
+        <v>91000</v>
       </c>
       <c r="H26" s="3">
-        <v>-669800</v>
+        <v>-676300</v>
       </c>
       <c r="I26" s="3">
-        <v>246800</v>
+        <v>249200</v>
       </c>
       <c r="J26" s="3">
-        <v>938300</v>
+        <v>947400</v>
       </c>
       <c r="K26" s="3">
         <v>207100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-564500</v>
+        <v>-569900</v>
       </c>
       <c r="E27" s="3">
-        <v>-654400</v>
+        <v>-660700</v>
       </c>
       <c r="F27" s="3">
-        <v>1901900</v>
+        <v>1920300</v>
       </c>
       <c r="G27" s="3">
-        <v>104700</v>
+        <v>105700</v>
       </c>
       <c r="H27" s="3">
-        <v>-594900</v>
+        <v>-600700</v>
       </c>
       <c r="I27" s="3">
-        <v>315100</v>
+        <v>318100</v>
       </c>
       <c r="J27" s="3">
-        <v>1003500</v>
+        <v>1013200</v>
       </c>
       <c r="K27" s="3">
         <v>245100</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-132400</v>
+        <v>-133700</v>
       </c>
       <c r="E32" s="3">
-        <v>-218300</v>
+        <v>-220400</v>
       </c>
       <c r="F32" s="3">
-        <v>-204500</v>
+        <v>-206500</v>
       </c>
       <c r="G32" s="3">
-        <v>-125400</v>
+        <v>-126600</v>
       </c>
       <c r="H32" s="3">
-        <v>-191400</v>
+        <v>-193300</v>
       </c>
       <c r="I32" s="3">
-        <v>-251600</v>
+        <v>-254000</v>
       </c>
       <c r="J32" s="3">
-        <v>-146500</v>
+        <v>-147900</v>
       </c>
       <c r="K32" s="3">
         <v>-79300</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-564500</v>
+        <v>-569900</v>
       </c>
       <c r="E33" s="3">
-        <v>-654400</v>
+        <v>-660700</v>
       </c>
       <c r="F33" s="3">
-        <v>1901900</v>
+        <v>1920300</v>
       </c>
       <c r="G33" s="3">
-        <v>104700</v>
+        <v>105700</v>
       </c>
       <c r="H33" s="3">
-        <v>-594900</v>
+        <v>-600700</v>
       </c>
       <c r="I33" s="3">
-        <v>315100</v>
+        <v>318100</v>
       </c>
       <c r="J33" s="3">
-        <v>1003500</v>
+        <v>1013200</v>
       </c>
       <c r="K33" s="3">
         <v>245100</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-564500</v>
+        <v>-569900</v>
       </c>
       <c r="E35" s="3">
-        <v>-654400</v>
+        <v>-660700</v>
       </c>
       <c r="F35" s="3">
-        <v>1901900</v>
+        <v>1920300</v>
       </c>
       <c r="G35" s="3">
-        <v>104700</v>
+        <v>105700</v>
       </c>
       <c r="H35" s="3">
-        <v>-594900</v>
+        <v>-600700</v>
       </c>
       <c r="I35" s="3">
-        <v>315100</v>
+        <v>318100</v>
       </c>
       <c r="J35" s="3">
-        <v>1003500</v>
+        <v>1013200</v>
       </c>
       <c r="K35" s="3">
         <v>245100</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2603900</v>
+        <v>2629100</v>
       </c>
       <c r="E41" s="3">
-        <v>2499800</v>
+        <v>2524000</v>
       </c>
       <c r="F41" s="3">
-        <v>2479100</v>
+        <v>2503100</v>
       </c>
       <c r="G41" s="3">
-        <v>2799400</v>
+        <v>2826500</v>
       </c>
       <c r="H41" s="3">
-        <v>2494700</v>
+        <v>2518900</v>
       </c>
       <c r="I41" s="3">
-        <v>2144800</v>
+        <v>2165500</v>
       </c>
       <c r="J41" s="3">
-        <v>3256700</v>
+        <v>3288200</v>
       </c>
       <c r="K41" s="3">
         <v>2514000</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>115200</v>
+        <v>116300</v>
       </c>
       <c r="E42" s="3">
-        <v>142400</v>
+        <v>143800</v>
       </c>
       <c r="F42" s="3">
-        <v>377900</v>
+        <v>381600</v>
       </c>
       <c r="G42" s="3">
-        <v>34700</v>
+        <v>35100</v>
       </c>
       <c r="H42" s="3">
-        <v>117200</v>
+        <v>118400</v>
       </c>
       <c r="I42" s="3">
-        <v>96100</v>
+        <v>97000</v>
       </c>
       <c r="J42" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="K42" s="3">
         <v>17600</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>755600</v>
+        <v>762900</v>
       </c>
       <c r="E43" s="3">
-        <v>617800</v>
+        <v>623800</v>
       </c>
       <c r="F43" s="3">
-        <v>1911900</v>
+        <v>1930400</v>
       </c>
       <c r="G43" s="3">
-        <v>1453700</v>
+        <v>1467700</v>
       </c>
       <c r="H43" s="3">
-        <v>997600</v>
+        <v>1007300</v>
       </c>
       <c r="I43" s="3">
-        <v>1472500</v>
+        <v>1486700</v>
       </c>
       <c r="J43" s="3">
-        <v>1261300</v>
+        <v>1273500</v>
       </c>
       <c r="K43" s="3">
         <v>1513900</v>
@@ -2034,25 +2034,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>899400</v>
+        <v>908100</v>
       </c>
       <c r="E44" s="3">
-        <v>938500</v>
+        <v>947600</v>
       </c>
       <c r="F44" s="3">
-        <v>1069500</v>
+        <v>1079900</v>
       </c>
       <c r="G44" s="3">
-        <v>829600</v>
+        <v>837600</v>
       </c>
       <c r="H44" s="3">
-        <v>727500</v>
+        <v>734500</v>
       </c>
       <c r="I44" s="3">
-        <v>815800</v>
+        <v>823700</v>
       </c>
       <c r="J44" s="3">
-        <v>770700</v>
+        <v>778200</v>
       </c>
       <c r="K44" s="3">
         <v>867700</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>97900</v>
+        <v>98900</v>
       </c>
       <c r="E45" s="3">
-        <v>148300</v>
+        <v>149800</v>
       </c>
       <c r="F45" s="3">
-        <v>116300</v>
+        <v>117500</v>
       </c>
       <c r="G45" s="3">
-        <v>102100</v>
+        <v>103100</v>
       </c>
       <c r="H45" s="3">
-        <v>103500</v>
+        <v>104500</v>
       </c>
       <c r="I45" s="3">
-        <v>93400</v>
+        <v>94300</v>
       </c>
       <c r="J45" s="3">
-        <v>282500</v>
+        <v>285200</v>
       </c>
       <c r="K45" s="3">
         <v>207700</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4472000</v>
+        <v>4515200</v>
       </c>
       <c r="E46" s="3">
-        <v>4346900</v>
+        <v>4388900</v>
       </c>
       <c r="F46" s="3">
-        <v>5954700</v>
+        <v>6012300</v>
       </c>
       <c r="G46" s="3">
-        <v>5219500</v>
+        <v>5270000</v>
       </c>
       <c r="H46" s="3">
-        <v>4440600</v>
+        <v>4483600</v>
       </c>
       <c r="I46" s="3">
-        <v>4622600</v>
+        <v>4667300</v>
       </c>
       <c r="J46" s="3">
-        <v>5587200</v>
+        <v>5641300</v>
       </c>
       <c r="K46" s="3">
         <v>5120900</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>993400</v>
+        <v>1003000</v>
       </c>
       <c r="E47" s="3">
-        <v>1043300</v>
+        <v>1053400</v>
       </c>
       <c r="F47" s="3">
-        <v>829700</v>
+        <v>837700</v>
       </c>
       <c r="G47" s="3">
-        <v>622900</v>
+        <v>628900</v>
       </c>
       <c r="H47" s="3">
-        <v>420000</v>
+        <v>424100</v>
       </c>
       <c r="I47" s="3">
-        <v>411400</v>
+        <v>415400</v>
       </c>
       <c r="J47" s="3">
-        <v>308400</v>
+        <v>311400</v>
       </c>
       <c r="K47" s="3">
         <v>257300</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5652000</v>
+        <v>5706700</v>
       </c>
       <c r="E48" s="3">
-        <v>5892800</v>
+        <v>5949800</v>
       </c>
       <c r="F48" s="3">
-        <v>5684100</v>
+        <v>5739100</v>
       </c>
       <c r="G48" s="3">
-        <v>6148700</v>
+        <v>6208100</v>
       </c>
       <c r="H48" s="3">
-        <v>6837600</v>
+        <v>6903800</v>
       </c>
       <c r="I48" s="3">
-        <v>6894000</v>
+        <v>6960700</v>
       </c>
       <c r="J48" s="3">
-        <v>6997400</v>
+        <v>7065100</v>
       </c>
       <c r="K48" s="3">
         <v>6997600</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>349400</v>
+        <v>352800</v>
       </c>
       <c r="E49" s="3">
-        <v>353400</v>
+        <v>356800</v>
       </c>
       <c r="F49" s="3">
-        <v>364600</v>
+        <v>368100</v>
       </c>
       <c r="G49" s="3">
-        <v>397000</v>
+        <v>400800</v>
       </c>
       <c r="H49" s="3">
-        <v>397200</v>
+        <v>401000</v>
       </c>
       <c r="I49" s="3">
-        <v>414800</v>
+        <v>418800</v>
       </c>
       <c r="J49" s="3">
-        <v>408400</v>
+        <v>412400</v>
       </c>
       <c r="K49" s="3">
         <v>426400</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>424600</v>
+        <v>428700</v>
       </c>
       <c r="E52" s="3">
-        <v>359600</v>
+        <v>363100</v>
       </c>
       <c r="F52" s="3">
-        <v>340300</v>
+        <v>343600</v>
       </c>
       <c r="G52" s="3">
-        <v>241400</v>
+        <v>243700</v>
       </c>
       <c r="H52" s="3">
-        <v>235300</v>
+        <v>237500</v>
       </c>
       <c r="I52" s="3">
-        <v>366100</v>
+        <v>369600</v>
       </c>
       <c r="J52" s="3">
-        <v>387900</v>
+        <v>391600</v>
       </c>
       <c r="K52" s="3">
         <v>671000</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11891400</v>
+        <v>12006500</v>
       </c>
       <c r="E54" s="3">
-        <v>11995900</v>
+        <v>12112000</v>
       </c>
       <c r="F54" s="3">
-        <v>13173400</v>
+        <v>13300800</v>
       </c>
       <c r="G54" s="3">
-        <v>12629500</v>
+        <v>12751600</v>
       </c>
       <c r="H54" s="3">
-        <v>12330700</v>
+        <v>12450000</v>
       </c>
       <c r="I54" s="3">
-        <v>12708900</v>
+        <v>12831800</v>
       </c>
       <c r="J54" s="3">
-        <v>13689400</v>
+        <v>13821800</v>
       </c>
       <c r="K54" s="3">
         <v>13473300</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1508200</v>
+        <v>1522800</v>
       </c>
       <c r="E57" s="3">
-        <v>1468900</v>
+        <v>1483100</v>
       </c>
       <c r="F57" s="3">
-        <v>1966000</v>
+        <v>1985000</v>
       </c>
       <c r="G57" s="3">
-        <v>1699700</v>
+        <v>1716200</v>
       </c>
       <c r="H57" s="3">
-        <v>1589500</v>
+        <v>1604900</v>
       </c>
       <c r="I57" s="3">
-        <v>1817800</v>
+        <v>1835400</v>
       </c>
       <c r="J57" s="3">
-        <v>1691700</v>
+        <v>1708100</v>
       </c>
       <c r="K57" s="3">
         <v>1880100</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>340200</v>
+        <v>343500</v>
       </c>
       <c r="E58" s="3">
-        <v>452600</v>
+        <v>457000</v>
       </c>
       <c r="F58" s="3">
-        <v>540000</v>
+        <v>545200</v>
       </c>
       <c r="G58" s="3">
-        <v>543400</v>
+        <v>548700</v>
       </c>
       <c r="H58" s="3">
-        <v>370400</v>
+        <v>373900</v>
       </c>
       <c r="I58" s="3">
-        <v>934700</v>
+        <v>943800</v>
       </c>
       <c r="J58" s="3">
-        <v>359100</v>
+        <v>362600</v>
       </c>
       <c r="K58" s="3">
         <v>583200</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1084400</v>
+        <v>1094900</v>
       </c>
       <c r="E59" s="3">
-        <v>1091600</v>
+        <v>1102200</v>
       </c>
       <c r="F59" s="3">
-        <v>1331600</v>
+        <v>1344500</v>
       </c>
       <c r="G59" s="3">
-        <v>806300</v>
+        <v>814100</v>
       </c>
       <c r="H59" s="3">
-        <v>847400</v>
+        <v>855600</v>
       </c>
       <c r="I59" s="3">
-        <v>1245800</v>
+        <v>1257900</v>
       </c>
       <c r="J59" s="3">
-        <v>1274600</v>
+        <v>1287000</v>
       </c>
       <c r="K59" s="3">
         <v>1213000</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2932800</v>
+        <v>2961100</v>
       </c>
       <c r="E60" s="3">
-        <v>3013200</v>
+        <v>3042300</v>
       </c>
       <c r="F60" s="3">
-        <v>3837600</v>
+        <v>3874800</v>
       </c>
       <c r="G60" s="3">
-        <v>3049500</v>
+        <v>3079000</v>
       </c>
       <c r="H60" s="3">
-        <v>2807300</v>
+        <v>2834400</v>
       </c>
       <c r="I60" s="3">
-        <v>3998400</v>
+        <v>4037000</v>
       </c>
       <c r="J60" s="3">
-        <v>3325400</v>
+        <v>3357600</v>
       </c>
       <c r="K60" s="3">
         <v>3676300</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3417600</v>
+        <v>3450600</v>
       </c>
       <c r="E61" s="3">
-        <v>2530200</v>
+        <v>2554700</v>
       </c>
       <c r="F61" s="3">
-        <v>1457800</v>
+        <v>1471900</v>
       </c>
       <c r="G61" s="3">
-        <v>3397700</v>
+        <v>3430600</v>
       </c>
       <c r="H61" s="3">
-        <v>3499200</v>
+        <v>3533100</v>
       </c>
       <c r="I61" s="3">
-        <v>1758600</v>
+        <v>1775600</v>
       </c>
       <c r="J61" s="3">
-        <v>3177100</v>
+        <v>3207800</v>
       </c>
       <c r="K61" s="3">
         <v>3329000</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>413300</v>
+        <v>417300</v>
       </c>
       <c r="E62" s="3">
-        <v>516900</v>
+        <v>521900</v>
       </c>
       <c r="F62" s="3">
-        <v>498600</v>
+        <v>503400</v>
       </c>
       <c r="G62" s="3">
-        <v>172900</v>
+        <v>174500</v>
       </c>
       <c r="H62" s="3">
-        <v>195100</v>
+        <v>197000</v>
       </c>
       <c r="I62" s="3">
-        <v>214100</v>
+        <v>216200</v>
       </c>
       <c r="J62" s="3">
-        <v>202100</v>
+        <v>204000</v>
       </c>
       <c r="K62" s="3">
         <v>209400</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6955700</v>
+        <v>7022900</v>
       </c>
       <c r="E66" s="3">
-        <v>6256000</v>
+        <v>6316500</v>
       </c>
       <c r="F66" s="3">
-        <v>5985700</v>
+        <v>6043600</v>
       </c>
       <c r="G66" s="3">
-        <v>6960700</v>
+        <v>7028000</v>
       </c>
       <c r="H66" s="3">
-        <v>6852100</v>
+        <v>6918400</v>
       </c>
       <c r="I66" s="3">
-        <v>6418100</v>
+        <v>6480200</v>
       </c>
       <c r="J66" s="3">
-        <v>7234500</v>
+        <v>7304500</v>
       </c>
       <c r="K66" s="3">
         <v>7791200</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>989200</v>
+        <v>998800</v>
       </c>
       <c r="E72" s="3">
-        <v>1552900</v>
+        <v>1568000</v>
       </c>
       <c r="F72" s="3">
-        <v>2501600</v>
+        <v>2525800</v>
       </c>
       <c r="G72" s="3">
-        <v>938300</v>
+        <v>947400</v>
       </c>
       <c r="H72" s="3">
-        <v>710200</v>
+        <v>717100</v>
       </c>
       <c r="I72" s="3">
-        <v>1452700</v>
+        <v>1466700</v>
       </c>
       <c r="J72" s="3">
-        <v>1585100</v>
+        <v>1600400</v>
       </c>
       <c r="K72" s="3">
         <v>760000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4935800</v>
+        <v>4983500</v>
       </c>
       <c r="E76" s="3">
-        <v>5739900</v>
+        <v>5795500</v>
       </c>
       <c r="F76" s="3">
-        <v>7187700</v>
+        <v>7257300</v>
       </c>
       <c r="G76" s="3">
-        <v>5668800</v>
+        <v>5723600</v>
       </c>
       <c r="H76" s="3">
-        <v>5478600</v>
+        <v>5531600</v>
       </c>
       <c r="I76" s="3">
-        <v>6290800</v>
+        <v>6351600</v>
       </c>
       <c r="J76" s="3">
-        <v>6454900</v>
+        <v>6517300</v>
       </c>
       <c r="K76" s="3">
         <v>5682000</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-564500</v>
+        <v>-569900</v>
       </c>
       <c r="E81" s="3">
-        <v>-654400</v>
+        <v>-660700</v>
       </c>
       <c r="F81" s="3">
-        <v>1901900</v>
+        <v>1920300</v>
       </c>
       <c r="G81" s="3">
-        <v>104700</v>
+        <v>105700</v>
       </c>
       <c r="H81" s="3">
-        <v>-594900</v>
+        <v>-600700</v>
       </c>
       <c r="I81" s="3">
-        <v>315100</v>
+        <v>318100</v>
       </c>
       <c r="J81" s="3">
-        <v>1003500</v>
+        <v>1013200</v>
       </c>
       <c r="K81" s="3">
         <v>245100</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1008000</v>
+        <v>1017700</v>
       </c>
       <c r="E83" s="3">
-        <v>975800</v>
+        <v>985200</v>
       </c>
       <c r="F83" s="3">
-        <v>1043900</v>
+        <v>1054000</v>
       </c>
       <c r="G83" s="3">
-        <v>1097700</v>
+        <v>1108300</v>
       </c>
       <c r="H83" s="3">
-        <v>1124400</v>
+        <v>1135200</v>
       </c>
       <c r="I83" s="3">
-        <v>1061400</v>
+        <v>1071700</v>
       </c>
       <c r="J83" s="3">
-        <v>1129700</v>
+        <v>1140600</v>
       </c>
       <c r="K83" s="3">
         <v>1244400</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>309900</v>
+        <v>312900</v>
       </c>
       <c r="E89" s="3">
-        <v>836400</v>
+        <v>844500</v>
       </c>
       <c r="F89" s="3">
-        <v>3247400</v>
+        <v>3278800</v>
       </c>
       <c r="G89" s="3">
-        <v>798400</v>
+        <v>806100</v>
       </c>
       <c r="H89" s="3">
-        <v>642900</v>
+        <v>649100</v>
       </c>
       <c r="I89" s="3">
-        <v>1246600</v>
+        <v>1258700</v>
       </c>
       <c r="J89" s="3">
-        <v>2616100</v>
+        <v>2641400</v>
       </c>
       <c r="K89" s="3">
         <v>1150400</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-830700</v>
+        <v>-838700</v>
       </c>
       <c r="E91" s="3">
-        <v>-1114800</v>
+        <v>-1125600</v>
       </c>
       <c r="F91" s="3">
-        <v>-528300</v>
+        <v>-533500</v>
       </c>
       <c r="G91" s="3">
-        <v>-483800</v>
+        <v>-488500</v>
       </c>
       <c r="H91" s="3">
-        <v>-916200</v>
+        <v>-925100</v>
       </c>
       <c r="I91" s="3">
-        <v>-1078200</v>
+        <v>-1088700</v>
       </c>
       <c r="J91" s="3">
-        <v>-1360800</v>
+        <v>-1373900</v>
       </c>
       <c r="K91" s="3">
         <v>-1449000</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-745900</v>
+        <v>-753100</v>
       </c>
       <c r="E94" s="3">
-        <v>-989600</v>
+        <v>-999200</v>
       </c>
       <c r="F94" s="3">
-        <v>-941200</v>
+        <v>-950300</v>
       </c>
       <c r="G94" s="3">
-        <v>-549100</v>
+        <v>-554400</v>
       </c>
       <c r="H94" s="3">
-        <v>-871800</v>
+        <v>-880200</v>
       </c>
       <c r="I94" s="3">
-        <v>-1069800</v>
+        <v>-1080100</v>
       </c>
       <c r="J94" s="3">
-        <v>-1354100</v>
+        <v>-1367200</v>
       </c>
       <c r="K94" s="3">
         <v>-1325100</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-190200</v>
+        <v>-192100</v>
       </c>
       <c r="E96" s="3">
-        <v>-296900</v>
+        <v>-299800</v>
       </c>
       <c r="F96" s="3">
-        <v>-88400</v>
+        <v>-89300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-149200</v>
+        <v>-150700</v>
       </c>
       <c r="I96" s="3">
-        <v>-447700</v>
+        <v>-452000</v>
       </c>
       <c r="J96" s="3">
-        <v>-167100</v>
+        <v>-168700</v>
       </c>
       <c r="K96" s="3">
         <v>-105600</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>569500</v>
+        <v>575100</v>
       </c>
       <c r="E100" s="3">
-        <v>73000</v>
+        <v>73700</v>
       </c>
       <c r="F100" s="3">
-        <v>-2588400</v>
+        <v>-2613500</v>
       </c>
       <c r="G100" s="3">
-        <v>83800</v>
+        <v>84600</v>
       </c>
       <c r="H100" s="3">
-        <v>643200</v>
+        <v>649400</v>
       </c>
       <c r="I100" s="3">
-        <v>-1297700</v>
+        <v>-1310200</v>
       </c>
       <c r="J100" s="3">
-        <v>-415900</v>
+        <v>-419900</v>
       </c>
       <c r="K100" s="3">
         <v>336100</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-29400</v>
+        <v>-29700</v>
       </c>
       <c r="E101" s="3">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="F101" s="3">
-        <v>-38200</v>
+        <v>-38500</v>
       </c>
       <c r="G101" s="3">
-        <v>-28500</v>
+        <v>-28700</v>
       </c>
       <c r="H101" s="3">
-        <v>-64300</v>
+        <v>-64900</v>
       </c>
       <c r="I101" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="J101" s="3">
-        <v>-76200</v>
+        <v>-76900</v>
       </c>
       <c r="K101" s="3">
         <v>-120400</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>104100</v>
+        <v>105100</v>
       </c>
       <c r="E102" s="3">
-        <v>20700</v>
+        <v>20900</v>
       </c>
       <c r="F102" s="3">
-        <v>-320300</v>
+        <v>-323400</v>
       </c>
       <c r="G102" s="3">
-        <v>304700</v>
+        <v>307600</v>
       </c>
       <c r="H102" s="3">
-        <v>350000</v>
+        <v>353400</v>
       </c>
       <c r="I102" s="3">
-        <v>-1111900</v>
+        <v>-1122700</v>
       </c>
       <c r="J102" s="3">
-        <v>770000</v>
+        <v>777400</v>
       </c>
       <c r="K102" s="3">
         <v>41100</v>

--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7763800</v>
+        <v>8093400</v>
       </c>
       <c r="E8" s="3">
-        <v>7727100</v>
+        <v>8033400</v>
       </c>
       <c r="F8" s="3">
-        <v>11606200</v>
+        <v>13375900</v>
       </c>
       <c r="G8" s="3">
-        <v>8483600</v>
+        <v>9644900</v>
       </c>
       <c r="H8" s="3">
-        <v>8415900</v>
+        <v>8985200</v>
       </c>
       <c r="I8" s="3">
-        <v>9632000</v>
+        <v>10050100</v>
       </c>
       <c r="J8" s="3">
-        <v>10677600</v>
+        <v>11495600</v>
       </c>
       <c r="K8" s="3">
         <v>10316900</v>
@@ -766,25 +766,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7619400</v>
+        <v>7942900</v>
       </c>
       <c r="E9" s="3">
-        <v>7678000</v>
+        <v>7982300</v>
       </c>
       <c r="F9" s="3">
-        <v>8764200</v>
+        <v>10100600</v>
       </c>
       <c r="G9" s="3">
-        <v>7770800</v>
+        <v>8834600</v>
       </c>
       <c r="H9" s="3">
-        <v>8401600</v>
+        <v>8969900</v>
       </c>
       <c r="I9" s="3">
-        <v>8751000</v>
+        <v>9130800</v>
       </c>
       <c r="J9" s="3">
-        <v>8766400</v>
+        <v>9438000</v>
       </c>
       <c r="K9" s="3">
         <v>9235600</v>
@@ -808,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>144400</v>
+        <v>150500</v>
       </c>
       <c r="E10" s="3">
-        <v>49100</v>
+        <v>51000</v>
       </c>
       <c r="F10" s="3">
-        <v>2841900</v>
+        <v>3275300</v>
       </c>
       <c r="G10" s="3">
-        <v>712800</v>
+        <v>810400</v>
       </c>
       <c r="H10" s="3">
-        <v>14300</v>
+        <v>15200</v>
       </c>
       <c r="I10" s="3">
-        <v>881000</v>
+        <v>919300</v>
       </c>
       <c r="J10" s="3">
-        <v>1911200</v>
+        <v>2057600</v>
       </c>
       <c r="K10" s="3">
         <v>1081300</v>
@@ -868,25 +868,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>414300</v>
+        <v>431900</v>
       </c>
       <c r="E12" s="3">
-        <v>402900</v>
+        <v>418900</v>
       </c>
       <c r="F12" s="3">
-        <v>409200</v>
+        <v>471600</v>
       </c>
       <c r="G12" s="3">
-        <v>322100</v>
+        <v>366100</v>
       </c>
       <c r="H12" s="3">
-        <v>307100</v>
+        <v>327900</v>
       </c>
       <c r="I12" s="3">
-        <v>298900</v>
+        <v>311900</v>
       </c>
       <c r="J12" s="3">
-        <v>308600</v>
+        <v>332200</v>
       </c>
       <c r="K12" s="3">
         <v>284700</v>
@@ -952,25 +952,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>39600</v>
+        <v>4600</v>
       </c>
       <c r="E14" s="3">
-        <v>33400</v>
+        <v>1400</v>
       </c>
       <c r="F14" s="3">
-        <v>32800</v>
+        <v>-60800</v>
       </c>
       <c r="G14" s="3">
-        <v>12400</v>
+        <v>17400</v>
       </c>
       <c r="H14" s="3">
-        <v>72000</v>
+        <v>60500</v>
       </c>
       <c r="I14" s="3">
-        <v>28200</v>
+        <v>-42200</v>
       </c>
       <c r="J14" s="3">
-        <v>51100</v>
+        <v>42400</v>
       </c>
       <c r="K14" s="3">
         <v>30600</v>
@@ -994,25 +994,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1039700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1003200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1189700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1232500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1182900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1118200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1228000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8491000</v>
+        <v>8810200</v>
       </c>
       <c r="E17" s="3">
-        <v>8511000</v>
+        <v>8813600</v>
       </c>
       <c r="F17" s="3">
-        <v>9664000</v>
+        <v>11099800</v>
       </c>
       <c r="G17" s="3">
-        <v>8430800</v>
+        <v>9570800</v>
       </c>
       <c r="H17" s="3">
-        <v>9128700</v>
+        <v>9669400</v>
       </c>
       <c r="I17" s="3">
-        <v>9451500</v>
+        <v>9831900</v>
       </c>
       <c r="J17" s="3">
-        <v>9503200</v>
+        <v>10176300</v>
       </c>
       <c r="K17" s="3">
         <v>9960700</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-727200</v>
+        <v>-716800</v>
       </c>
       <c r="E18" s="3">
-        <v>-783900</v>
+        <v>-780300</v>
       </c>
       <c r="F18" s="3">
-        <v>1942100</v>
+        <v>2276000</v>
       </c>
       <c r="G18" s="3">
-        <v>52800</v>
+        <v>74100</v>
       </c>
       <c r="H18" s="3">
-        <v>-712800</v>
+        <v>-684200</v>
       </c>
       <c r="I18" s="3">
-        <v>180600</v>
+        <v>218200</v>
       </c>
       <c r="J18" s="3">
-        <v>1174400</v>
+        <v>1319300</v>
       </c>
       <c r="K18" s="3">
         <v>356200</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>133700</v>
+        <v>-38000</v>
       </c>
       <c r="E20" s="3">
-        <v>220400</v>
+        <v>-161800</v>
       </c>
       <c r="F20" s="3">
-        <v>206500</v>
+        <v>-118300</v>
       </c>
       <c r="G20" s="3">
-        <v>126600</v>
+        <v>-116300</v>
       </c>
       <c r="H20" s="3">
-        <v>193300</v>
+        <v>-139500</v>
       </c>
       <c r="I20" s="3">
-        <v>254000</v>
+        <v>-150200</v>
       </c>
       <c r="J20" s="3">
-        <v>147900</v>
+        <v>-117600</v>
       </c>
       <c r="K20" s="3">
         <v>79300</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>420300</v>
+        <v>360900</v>
       </c>
       <c r="E21" s="3">
-        <v>417900</v>
+        <v>384800</v>
       </c>
       <c r="F21" s="3">
-        <v>3198600</v>
+        <v>3584100</v>
       </c>
       <c r="G21" s="3">
-        <v>1283500</v>
+        <v>1422900</v>
       </c>
       <c r="H21" s="3">
-        <v>611300</v>
+        <v>638200</v>
       </c>
       <c r="I21" s="3">
-        <v>1502100</v>
+        <v>1486600</v>
       </c>
       <c r="J21" s="3">
-        <v>2458500</v>
+        <v>2664900</v>
       </c>
       <c r="K21" s="3">
         <v>1677200</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>85300</v>
+        <v>86800</v>
       </c>
       <c r="E22" s="3">
-        <v>47200</v>
+        <v>43900</v>
       </c>
       <c r="F22" s="3">
-        <v>69400</v>
+        <v>77100</v>
       </c>
       <c r="G22" s="3">
-        <v>92200</v>
+        <v>102000</v>
       </c>
       <c r="H22" s="3">
-        <v>101800</v>
+        <v>97700</v>
       </c>
       <c r="I22" s="3">
-        <v>83400</v>
+        <v>87000</v>
       </c>
       <c r="J22" s="3">
-        <v>89800</v>
+        <v>96700</v>
       </c>
       <c r="K22" s="3">
         <v>84900</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-678900</v>
+        <v>-707700</v>
       </c>
       <c r="E23" s="3">
-        <v>-610700</v>
+        <v>-634900</v>
       </c>
       <c r="F23" s="3">
-        <v>2079200</v>
+        <v>2396200</v>
       </c>
       <c r="G23" s="3">
-        <v>87300</v>
+        <v>99200</v>
       </c>
       <c r="H23" s="3">
-        <v>-621300</v>
+        <v>-663400</v>
       </c>
       <c r="I23" s="3">
-        <v>351200</v>
+        <v>366400</v>
       </c>
       <c r="J23" s="3">
-        <v>1232500</v>
+        <v>1326900</v>
       </c>
       <c r="K23" s="3">
         <v>350700</v>
@@ -1321,25 +1321,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-110600</v>
+        <v>-115200</v>
       </c>
       <c r="E24" s="3">
-        <v>45900</v>
+        <v>47800</v>
       </c>
       <c r="F24" s="3">
-        <v>92300</v>
+        <v>106400</v>
       </c>
       <c r="G24" s="3">
-        <v>-3700</v>
+        <v>-4300</v>
       </c>
       <c r="H24" s="3">
-        <v>54900</v>
+        <v>58700</v>
       </c>
       <c r="I24" s="3">
-        <v>102000</v>
+        <v>10500</v>
       </c>
       <c r="J24" s="3">
-        <v>285100</v>
+        <v>-37900</v>
       </c>
       <c r="K24" s="3">
         <v>143600</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-568300</v>
+        <v>-592400</v>
       </c>
       <c r="E26" s="3">
-        <v>-656700</v>
+        <v>-682700</v>
       </c>
       <c r="F26" s="3">
-        <v>1986900</v>
+        <v>2289900</v>
       </c>
       <c r="G26" s="3">
-        <v>91000</v>
+        <v>103500</v>
       </c>
       <c r="H26" s="3">
-        <v>-676300</v>
+        <v>-722000</v>
       </c>
       <c r="I26" s="3">
-        <v>249200</v>
+        <v>355900</v>
       </c>
       <c r="J26" s="3">
-        <v>947400</v>
+        <v>1364800</v>
       </c>
       <c r="K26" s="3">
         <v>207100</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-569900</v>
+        <v>-594100</v>
       </c>
       <c r="E27" s="3">
-        <v>-660700</v>
+        <v>-686900</v>
       </c>
       <c r="F27" s="3">
-        <v>1920300</v>
+        <v>2213100</v>
       </c>
       <c r="G27" s="3">
-        <v>105700</v>
+        <v>120200</v>
       </c>
       <c r="H27" s="3">
-        <v>-600700</v>
+        <v>-641300</v>
       </c>
       <c r="I27" s="3">
-        <v>318100</v>
+        <v>427000</v>
       </c>
       <c r="J27" s="3">
-        <v>1013200</v>
+        <v>1436300</v>
       </c>
       <c r="K27" s="3">
         <v>245100</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-133700</v>
+        <v>38000</v>
       </c>
       <c r="E32" s="3">
-        <v>-220400</v>
+        <v>161800</v>
       </c>
       <c r="F32" s="3">
-        <v>-206500</v>
+        <v>118300</v>
       </c>
       <c r="G32" s="3">
-        <v>-126600</v>
+        <v>116300</v>
       </c>
       <c r="H32" s="3">
-        <v>-193300</v>
+        <v>139500</v>
       </c>
       <c r="I32" s="3">
-        <v>-254000</v>
+        <v>150200</v>
       </c>
       <c r="J32" s="3">
-        <v>-147900</v>
+        <v>117600</v>
       </c>
       <c r="K32" s="3">
         <v>-79300</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-569900</v>
+        <v>-594100</v>
       </c>
       <c r="E33" s="3">
-        <v>-660700</v>
+        <v>-686900</v>
       </c>
       <c r="F33" s="3">
-        <v>1920300</v>
+        <v>2213100</v>
       </c>
       <c r="G33" s="3">
-        <v>105700</v>
+        <v>120200</v>
       </c>
       <c r="H33" s="3">
-        <v>-600700</v>
+        <v>-641300</v>
       </c>
       <c r="I33" s="3">
-        <v>318100</v>
+        <v>427000</v>
       </c>
       <c r="J33" s="3">
-        <v>1013200</v>
+        <v>1436300</v>
       </c>
       <c r="K33" s="3">
         <v>245100</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-569900</v>
+        <v>-594100</v>
       </c>
       <c r="E35" s="3">
-        <v>-660700</v>
+        <v>-686900</v>
       </c>
       <c r="F35" s="3">
-        <v>1920300</v>
+        <v>2213100</v>
       </c>
       <c r="G35" s="3">
-        <v>105700</v>
+        <v>120200</v>
       </c>
       <c r="H35" s="3">
-        <v>-600700</v>
+        <v>-641300</v>
       </c>
       <c r="I35" s="3">
-        <v>318100</v>
+        <v>427000</v>
       </c>
       <c r="J35" s="3">
-        <v>1013200</v>
+        <v>1436300</v>
       </c>
       <c r="K35" s="3">
         <v>245100</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2629100</v>
+        <v>2740700</v>
       </c>
       <c r="E41" s="3">
-        <v>2524000</v>
+        <v>2624000</v>
       </c>
       <c r="F41" s="3">
-        <v>2503100</v>
+        <v>2884700</v>
       </c>
       <c r="G41" s="3">
-        <v>2826500</v>
+        <v>3213400</v>
       </c>
       <c r="H41" s="3">
-        <v>2518900</v>
+        <v>2689300</v>
       </c>
       <c r="I41" s="3">
-        <v>2165500</v>
+        <v>2259500</v>
       </c>
       <c r="J41" s="3">
-        <v>3288200</v>
+        <v>3540100</v>
       </c>
       <c r="K41" s="3">
         <v>2514000</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>116300</v>
+        <v>19100</v>
       </c>
       <c r="E42" s="3">
-        <v>143800</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>381600</v>
+        <v>360800</v>
       </c>
       <c r="G42" s="3">
-        <v>35100</v>
+        <v>34700</v>
       </c>
       <c r="H42" s="3">
-        <v>118400</v>
+        <v>126400</v>
       </c>
       <c r="I42" s="3">
-        <v>97000</v>
+        <v>101200</v>
       </c>
       <c r="J42" s="3">
-        <v>16200</v>
+        <v>13400</v>
       </c>
       <c r="K42" s="3">
         <v>17600</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>762900</v>
+        <v>838300</v>
       </c>
       <c r="E43" s="3">
-        <v>623800</v>
+        <v>677100</v>
       </c>
       <c r="F43" s="3">
-        <v>1930400</v>
+        <v>2274200</v>
       </c>
       <c r="G43" s="3">
-        <v>1467700</v>
+        <v>1673800</v>
       </c>
       <c r="H43" s="3">
-        <v>1007300</v>
+        <v>1075400</v>
       </c>
       <c r="I43" s="3">
-        <v>1486700</v>
+        <v>1551300</v>
       </c>
       <c r="J43" s="3">
-        <v>1273500</v>
+        <v>1377400</v>
       </c>
       <c r="K43" s="3">
         <v>1513900</v>
@@ -2034,25 +2034,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>908100</v>
+        <v>946600</v>
       </c>
       <c r="E44" s="3">
-        <v>947600</v>
+        <v>985100</v>
       </c>
       <c r="F44" s="3">
-        <v>1079900</v>
+        <v>1244500</v>
       </c>
       <c r="G44" s="3">
-        <v>837600</v>
+        <v>952300</v>
       </c>
       <c r="H44" s="3">
-        <v>734500</v>
+        <v>784200</v>
       </c>
       <c r="I44" s="3">
-        <v>823700</v>
+        <v>859500</v>
       </c>
       <c r="J44" s="3">
-        <v>778200</v>
+        <v>837800</v>
       </c>
       <c r="K44" s="3">
         <v>867700</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>98900</v>
+        <v>162200</v>
       </c>
       <c r="E45" s="3">
-        <v>149800</v>
+        <v>276700</v>
       </c>
       <c r="F45" s="3">
-        <v>117500</v>
+        <v>164800</v>
       </c>
       <c r="G45" s="3">
-        <v>103100</v>
+        <v>117200</v>
       </c>
       <c r="H45" s="3">
-        <v>104500</v>
+        <v>111600</v>
       </c>
       <c r="I45" s="3">
-        <v>94300</v>
+        <v>98400</v>
       </c>
       <c r="J45" s="3">
-        <v>285200</v>
+        <v>304700</v>
       </c>
       <c r="K45" s="3">
         <v>207700</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4515200</v>
+        <v>4706900</v>
       </c>
       <c r="E46" s="3">
-        <v>4388900</v>
+        <v>4562900</v>
       </c>
       <c r="F46" s="3">
-        <v>6012300</v>
+        <v>6929100</v>
       </c>
       <c r="G46" s="3">
-        <v>5270000</v>
+        <v>5991400</v>
       </c>
       <c r="H46" s="3">
-        <v>4483600</v>
+        <v>4786900</v>
       </c>
       <c r="I46" s="3">
-        <v>4667300</v>
+        <v>4869900</v>
       </c>
       <c r="J46" s="3">
-        <v>5641300</v>
+        <v>6073500</v>
       </c>
       <c r="K46" s="3">
         <v>5120900</v>
@@ -2160,25 +2160,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1003000</v>
+        <v>1045600</v>
       </c>
       <c r="E47" s="3">
-        <v>1053400</v>
+        <v>1132300</v>
       </c>
       <c r="F47" s="3">
-        <v>837700</v>
+        <v>990900</v>
       </c>
       <c r="G47" s="3">
-        <v>628900</v>
+        <v>715000</v>
       </c>
       <c r="H47" s="3">
-        <v>424100</v>
+        <v>452800</v>
       </c>
       <c r="I47" s="3">
-        <v>415400</v>
+        <v>433400</v>
       </c>
       <c r="J47" s="3">
-        <v>311400</v>
+        <v>335200</v>
       </c>
       <c r="K47" s="3">
         <v>257300</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5706700</v>
+        <v>5906500</v>
       </c>
       <c r="E48" s="3">
-        <v>5949800</v>
+        <v>6141000</v>
       </c>
       <c r="F48" s="3">
-        <v>5739100</v>
+        <v>6562300</v>
       </c>
       <c r="G48" s="3">
-        <v>6208100</v>
+        <v>7003800</v>
       </c>
       <c r="H48" s="3">
-        <v>6903800</v>
+        <v>7318800</v>
       </c>
       <c r="I48" s="3">
-        <v>6960700</v>
+        <v>7239000</v>
       </c>
       <c r="J48" s="3">
-        <v>7065100</v>
+        <v>7582200</v>
       </c>
       <c r="K48" s="3">
         <v>6997600</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>352800</v>
+        <v>367800</v>
       </c>
       <c r="E49" s="3">
-        <v>356800</v>
+        <v>371000</v>
       </c>
       <c r="F49" s="3">
-        <v>368100</v>
+        <v>424200</v>
       </c>
       <c r="G49" s="3">
-        <v>400800</v>
+        <v>455700</v>
       </c>
       <c r="H49" s="3">
-        <v>401000</v>
+        <v>428200</v>
       </c>
       <c r="I49" s="3">
-        <v>418800</v>
+        <v>68500</v>
       </c>
       <c r="J49" s="3">
-        <v>412400</v>
+        <v>63700</v>
       </c>
       <c r="K49" s="3">
         <v>426400</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>428700</v>
+        <v>156400</v>
       </c>
       <c r="E52" s="3">
-        <v>363100</v>
+        <v>168500</v>
       </c>
       <c r="F52" s="3">
-        <v>343600</v>
+        <v>189000</v>
       </c>
       <c r="G52" s="3">
-        <v>243700</v>
+        <v>117500</v>
       </c>
       <c r="H52" s="3">
-        <v>237500</v>
+        <v>132400</v>
       </c>
       <c r="I52" s="3">
-        <v>369600</v>
+        <v>192800</v>
       </c>
       <c r="J52" s="3">
-        <v>391600</v>
+        <v>207600</v>
       </c>
       <c r="K52" s="3">
         <v>671000</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12006500</v>
+        <v>12516200</v>
       </c>
       <c r="E54" s="3">
-        <v>12112000</v>
+        <v>12592100</v>
       </c>
       <c r="F54" s="3">
-        <v>13300800</v>
+        <v>15328900</v>
       </c>
       <c r="G54" s="3">
-        <v>12751600</v>
+        <v>14497200</v>
       </c>
       <c r="H54" s="3">
-        <v>12450000</v>
+        <v>13292200</v>
       </c>
       <c r="I54" s="3">
-        <v>12831800</v>
+        <v>13020300</v>
       </c>
       <c r="J54" s="3">
-        <v>13821800</v>
+        <v>14500500</v>
       </c>
       <c r="K54" s="3">
         <v>13473300</v>
@@ -2532,25 +2532,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1522800</v>
+        <v>1587500</v>
       </c>
       <c r="E57" s="3">
-        <v>1483100</v>
+        <v>1541900</v>
       </c>
       <c r="F57" s="3">
-        <v>1985000</v>
+        <v>2287700</v>
       </c>
       <c r="G57" s="3">
-        <v>1716200</v>
+        <v>1951100</v>
       </c>
       <c r="H57" s="3">
-        <v>1604900</v>
+        <v>1713500</v>
       </c>
       <c r="I57" s="3">
-        <v>1835400</v>
+        <v>1915100</v>
       </c>
       <c r="J57" s="3">
-        <v>1708100</v>
+        <v>1838900</v>
       </c>
       <c r="K57" s="3">
         <v>1880100</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>343500</v>
+        <v>358000</v>
       </c>
       <c r="E58" s="3">
-        <v>457000</v>
+        <v>475100</v>
       </c>
       <c r="F58" s="3">
-        <v>545200</v>
+        <v>628400</v>
       </c>
       <c r="G58" s="3">
-        <v>548700</v>
+        <v>623800</v>
       </c>
       <c r="H58" s="3">
-        <v>373900</v>
+        <v>399200</v>
       </c>
       <c r="I58" s="3">
-        <v>943800</v>
+        <v>984700</v>
       </c>
       <c r="J58" s="3">
-        <v>362600</v>
+        <v>390300</v>
       </c>
       <c r="K58" s="3">
         <v>583200</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1094900</v>
+        <v>1141400</v>
       </c>
       <c r="E59" s="3">
-        <v>1102200</v>
+        <v>1145900</v>
       </c>
       <c r="F59" s="3">
-        <v>1344500</v>
+        <v>1549500</v>
       </c>
       <c r="G59" s="3">
-        <v>814100</v>
+        <v>925600</v>
       </c>
       <c r="H59" s="3">
-        <v>855600</v>
+        <v>913500</v>
       </c>
       <c r="I59" s="3">
-        <v>1257900</v>
+        <v>1326400</v>
       </c>
       <c r="J59" s="3">
-        <v>1287000</v>
+        <v>1487600</v>
       </c>
       <c r="K59" s="3">
         <v>1213000</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2961100</v>
+        <v>3086900</v>
       </c>
       <c r="E60" s="3">
-        <v>3042300</v>
+        <v>3162900</v>
       </c>
       <c r="F60" s="3">
-        <v>3874800</v>
+        <v>4465600</v>
       </c>
       <c r="G60" s="3">
-        <v>3079000</v>
+        <v>3500500</v>
       </c>
       <c r="H60" s="3">
-        <v>2834400</v>
+        <v>3026200</v>
       </c>
       <c r="I60" s="3">
-        <v>4037000</v>
+        <v>4226200</v>
       </c>
       <c r="J60" s="3">
-        <v>3357600</v>
+        <v>3716900</v>
       </c>
       <c r="K60" s="3">
         <v>3676300</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3450600</v>
+        <v>3597100</v>
       </c>
       <c r="E61" s="3">
-        <v>2554700</v>
+        <v>2655900</v>
       </c>
       <c r="F61" s="3">
-        <v>1471900</v>
+        <v>1696400</v>
       </c>
       <c r="G61" s="3">
-        <v>3430600</v>
+        <v>3900200</v>
       </c>
       <c r="H61" s="3">
-        <v>3533100</v>
+        <v>3772100</v>
       </c>
       <c r="I61" s="3">
-        <v>1775600</v>
+        <v>1852600</v>
       </c>
       <c r="J61" s="3">
-        <v>3207800</v>
+        <v>3453500</v>
       </c>
       <c r="K61" s="3">
         <v>3329000</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>417300</v>
+        <v>101900</v>
       </c>
       <c r="E62" s="3">
-        <v>521900</v>
+        <v>91000</v>
       </c>
       <c r="F62" s="3">
-        <v>503400</v>
+        <v>111100</v>
       </c>
       <c r="G62" s="3">
-        <v>174500</v>
+        <v>84000</v>
       </c>
       <c r="H62" s="3">
-        <v>197000</v>
+        <v>80700</v>
       </c>
       <c r="I62" s="3">
-        <v>216200</v>
+        <v>70900</v>
       </c>
       <c r="J62" s="3">
-        <v>204000</v>
+        <v>70200</v>
       </c>
       <c r="K62" s="3">
         <v>209400</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7022900</v>
+        <v>7119000</v>
       </c>
       <c r="E66" s="3">
-        <v>6316500</v>
+        <v>6361400</v>
       </c>
       <c r="F66" s="3">
-        <v>6043600</v>
+        <v>6742100</v>
       </c>
       <c r="G66" s="3">
-        <v>7028000</v>
+        <v>7599000</v>
       </c>
       <c r="H66" s="3">
-        <v>6918400</v>
+        <v>7008600</v>
       </c>
       <c r="I66" s="3">
-        <v>6480200</v>
+        <v>6232100</v>
       </c>
       <c r="J66" s="3">
-        <v>7304500</v>
+        <v>7326700</v>
       </c>
       <c r="K66" s="3">
         <v>7791200</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>998800</v>
+        <v>1041200</v>
       </c>
       <c r="E72" s="3">
-        <v>1568000</v>
+        <v>1630100</v>
       </c>
       <c r="F72" s="3">
-        <v>2525800</v>
+        <v>2910900</v>
       </c>
       <c r="G72" s="3">
-        <v>947400</v>
+        <v>1077100</v>
       </c>
       <c r="H72" s="3">
-        <v>717100</v>
+        <v>765600</v>
       </c>
       <c r="I72" s="3">
-        <v>1466700</v>
+        <v>1220300</v>
       </c>
       <c r="J72" s="3">
-        <v>1600400</v>
+        <v>1304900</v>
       </c>
       <c r="K72" s="3">
         <v>760000</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4983500</v>
+        <v>5195100</v>
       </c>
       <c r="E76" s="3">
-        <v>5795500</v>
+        <v>6025200</v>
       </c>
       <c r="F76" s="3">
-        <v>7257300</v>
+        <v>8363800</v>
       </c>
       <c r="G76" s="3">
-        <v>5723600</v>
+        <v>6507100</v>
       </c>
       <c r="H76" s="3">
-        <v>5531600</v>
+        <v>5905800</v>
       </c>
       <c r="I76" s="3">
-        <v>6351600</v>
+        <v>6317200</v>
       </c>
       <c r="J76" s="3">
-        <v>6517300</v>
+        <v>6598400</v>
       </c>
       <c r="K76" s="3">
         <v>5682000</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-569900</v>
+        <v>-594100</v>
       </c>
       <c r="E81" s="3">
-        <v>-660700</v>
+        <v>-686900</v>
       </c>
       <c r="F81" s="3">
-        <v>1920300</v>
+        <v>2213100</v>
       </c>
       <c r="G81" s="3">
-        <v>105700</v>
+        <v>120200</v>
       </c>
       <c r="H81" s="3">
-        <v>-600700</v>
+        <v>-641300</v>
       </c>
       <c r="I81" s="3">
-        <v>318100</v>
+        <v>427000</v>
       </c>
       <c r="J81" s="3">
-        <v>1013200</v>
+        <v>1436300</v>
       </c>
       <c r="K81" s="3">
         <v>245100</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1017700</v>
+        <v>1058300</v>
       </c>
       <c r="E83" s="3">
-        <v>985200</v>
+        <v>1019700</v>
       </c>
       <c r="F83" s="3">
-        <v>1054000</v>
+        <v>1207300</v>
       </c>
       <c r="G83" s="3">
-        <v>1108300</v>
+        <v>1250500</v>
       </c>
       <c r="H83" s="3">
-        <v>1135200</v>
+        <v>1193100</v>
       </c>
       <c r="I83" s="3">
-        <v>1071700</v>
+        <v>1100500</v>
       </c>
       <c r="J83" s="3">
-        <v>1140600</v>
+        <v>1206800</v>
       </c>
       <c r="K83" s="3">
         <v>1244400</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>312900</v>
+        <v>326200</v>
       </c>
       <c r="E89" s="3">
-        <v>844500</v>
+        <v>877900</v>
       </c>
       <c r="F89" s="3">
-        <v>3278800</v>
+        <v>3778800</v>
       </c>
       <c r="G89" s="3">
-        <v>806100</v>
+        <v>916500</v>
       </c>
       <c r="H89" s="3">
-        <v>649100</v>
+        <v>693000</v>
       </c>
       <c r="I89" s="3">
-        <v>1258700</v>
+        <v>1313300</v>
       </c>
       <c r="J89" s="3">
-        <v>2641400</v>
+        <v>2843800</v>
       </c>
       <c r="K89" s="3">
         <v>1150400</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-838700</v>
+        <v>-874300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1125600</v>
+        <v>-1170200</v>
       </c>
       <c r="F91" s="3">
-        <v>-533500</v>
+        <v>-614600</v>
       </c>
       <c r="G91" s="3">
-        <v>-488500</v>
+        <v>-555300</v>
       </c>
       <c r="H91" s="3">
-        <v>-925100</v>
+        <v>-987700</v>
       </c>
       <c r="I91" s="3">
-        <v>-1088700</v>
+        <v>-1135900</v>
       </c>
       <c r="J91" s="3">
-        <v>-1373900</v>
+        <v>-1479200</v>
       </c>
       <c r="K91" s="3">
         <v>-1449000</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-753100</v>
+        <v>-785100</v>
       </c>
       <c r="E94" s="3">
-        <v>-999200</v>
+        <v>-1038800</v>
       </c>
       <c r="F94" s="3">
-        <v>-950300</v>
+        <v>-1095200</v>
       </c>
       <c r="G94" s="3">
-        <v>-554400</v>
+        <v>-630300</v>
       </c>
       <c r="H94" s="3">
-        <v>-880200</v>
+        <v>-939700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1080100</v>
+        <v>-1127000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1367200</v>
+        <v>-1472000</v>
       </c>
       <c r="K94" s="3">
         <v>-1325100</v>
@@ -3995,25 +3995,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-192100</v>
+        <v>200200</v>
       </c>
       <c r="E96" s="3">
-        <v>-299800</v>
+        <v>311700</v>
       </c>
       <c r="F96" s="3">
-        <v>-89300</v>
+        <v>102900</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-150700</v>
+        <v>160900</v>
       </c>
       <c r="I96" s="3">
-        <v>-452000</v>
+        <v>471600</v>
       </c>
       <c r="J96" s="3">
-        <v>-168700</v>
+        <v>181700</v>
       </c>
       <c r="K96" s="3">
         <v>-105600</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>575100</v>
+        <v>599500</v>
       </c>
       <c r="E100" s="3">
-        <v>73700</v>
+        <v>76600</v>
       </c>
       <c r="F100" s="3">
-        <v>-2613500</v>
+        <v>-3012000</v>
       </c>
       <c r="G100" s="3">
-        <v>84600</v>
+        <v>96200</v>
       </c>
       <c r="H100" s="3">
-        <v>649400</v>
+        <v>693400</v>
       </c>
       <c r="I100" s="3">
-        <v>-1310200</v>
+        <v>-1367100</v>
       </c>
       <c r="J100" s="3">
-        <v>-419900</v>
+        <v>-452000</v>
       </c>
       <c r="K100" s="3">
         <v>336100</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-29700</v>
+        <v>-31000</v>
       </c>
       <c r="E101" s="3">
-        <v>102000</v>
+        <v>106000</v>
       </c>
       <c r="F101" s="3">
-        <v>-38500</v>
+        <v>-44400</v>
       </c>
       <c r="G101" s="3">
-        <v>-28700</v>
+        <v>-32700</v>
       </c>
       <c r="H101" s="3">
-        <v>-64900</v>
+        <v>-69300</v>
       </c>
       <c r="I101" s="3">
-        <v>9000</v>
+        <v>9400</v>
       </c>
       <c r="J101" s="3">
-        <v>-76900</v>
+        <v>-82800</v>
       </c>
       <c r="K101" s="3">
         <v>-120400</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>105100</v>
+        <v>109500</v>
       </c>
       <c r="E102" s="3">
-        <v>20900</v>
+        <v>21800</v>
       </c>
       <c r="F102" s="3">
-        <v>-323400</v>
+        <v>-372700</v>
       </c>
       <c r="G102" s="3">
-        <v>307600</v>
+        <v>349700</v>
       </c>
       <c r="H102" s="3">
-        <v>353400</v>
+        <v>377300</v>
       </c>
       <c r="I102" s="3">
-        <v>-1122700</v>
+        <v>-1171400</v>
       </c>
       <c r="J102" s="3">
-        <v>777400</v>
+        <v>837000</v>
       </c>
       <c r="K102" s="3">
         <v>41100</v>

--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8549300</v>
+      </c>
+      <c r="E8" s="3">
         <v>8093400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8033400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13375900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9644900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8985200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10050100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11495600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10316900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11487800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14702600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14606000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12587900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7810500</v>
+      </c>
+      <c r="E9" s="3">
         <v>7942900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7982300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10100600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8834600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8969900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9130800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9438000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9235600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10217800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12955200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26827700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25900900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>738700</v>
+      </c>
+      <c r="E10" s="3">
         <v>150500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3275300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>810400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>919300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2057600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1081300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1270000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1747400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-12221700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-13312900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E12" s="3">
         <v>431900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>418900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>471600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>366100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>327900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>311900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>332200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>284700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>283900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>329800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>299200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>329400</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4600</v>
+        <v>-210000</v>
       </c>
       <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-60800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>60500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-42200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>42400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>383500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>82600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>140400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>800400</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>968700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1039700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1003200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1189700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1232500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1182900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1118200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1228000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19800</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8807500</v>
+      </c>
+      <c r="E17" s="3">
         <v>8810200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8813600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11099800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9570800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9669400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9831900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10176300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9960700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11312800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13986800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14455500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14139900</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-258300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-716800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-780300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2276000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>74100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-684200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>218200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1319300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>356200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>175100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>715800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>150500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1552000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-38000</v>
+        <v>-76100</v>
       </c>
       <c r="E20" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-161800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-118300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-116300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-139500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-150200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-117600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>79300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>149800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>149600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>368800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>220500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>360900</v>
+        <v>786600</v>
       </c>
       <c r="E21" s="3">
+        <v>356600</v>
+      </c>
+      <c r="F21" s="3">
         <v>384800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3584100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1422900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>638200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1486600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2664900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1677200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1820300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2908200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2752300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1176800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E22" s="3">
         <v>86800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>77100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>102000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>87000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>96700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>82600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>145700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>335600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>381200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-707700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-634900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2396200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>99200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-663400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>366400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1326900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>350700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>242300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>719700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>183700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1712700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-115200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>106400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-37900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>143600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>116800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>47700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-592400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-682700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2289900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>103500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-722000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>355900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1364800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>207100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>154400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>602900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>136000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1750100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-594100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-686900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2213100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>120200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-641300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>427000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1436300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>245100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>157200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>589500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>133400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1702400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>38000</v>
+        <v>76100</v>
       </c>
       <c r="E32" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F32" s="3">
         <v>161800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>118300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>116300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>139500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>150200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>117600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-79300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-149800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-149600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-368800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-220500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-594100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-686900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2213100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>120200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-641300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>427000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1436300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>245100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>157200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>589500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>133400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1702400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-594100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-686900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2213100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>120200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-641300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>427000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1436300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>245100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>157200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>589500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>133400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1702400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,386 +1987,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2088100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2740700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2624000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2884700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3213400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2689300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2259500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3540100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2514000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2514700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2952400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2677000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2398600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E42" s="3">
         <v>19100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>360800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>34700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>126400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>101200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>374100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>108900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>238500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>181200</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>829800</v>
+      </c>
+      <c r="E43" s="3">
         <v>838300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>677100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2274200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1673800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1075400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1551300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1377400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1513900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1111600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2149100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1535600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1418200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1031500</v>
+      </c>
+      <c r="E44" s="3">
         <v>946600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>985100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1244500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>952300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>784200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>859500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>837800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>867700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1013600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1311900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1318900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1416400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E45" s="3">
         <v>162200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>276700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>164800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>117200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>98400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>304700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>207700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>150200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>163600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>179600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>430500</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4213900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4706900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4562900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6929100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5991400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4786900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4869900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6073500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5120900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5164300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6685800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5949700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5845000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>932700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1045600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1132300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>990900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>715000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>452800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>433400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>335200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>257300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>463800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>535800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>493000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>511800</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5373100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5906500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6141000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6562300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7003800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7318800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7239000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7582200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6997600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6670900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8366700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9525100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10554300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>592400</v>
+      </c>
+      <c r="E49" s="3">
         <v>367800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>371000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>424200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>455700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>428200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>68500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>426400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>464700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>140000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>155500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>496700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>272500</v>
+      </c>
+      <c r="E52" s="3">
         <v>156400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>168500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>189000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>117500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>132400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>192800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>207600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>671000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>802900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>204900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>183100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>546100</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11985000</v>
+      </c>
+      <c r="E54" s="3">
         <v>12516200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12592100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15328900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14497200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13292200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13020300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14500500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13473300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13566700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15933200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16306400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17953800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1651500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1587500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1541900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2287700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1951100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1713500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1915100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1838900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1880100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1957900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2695200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2749000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2711000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>521600</v>
+      </c>
+      <c r="E58" s="3">
         <v>358000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>475100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>628400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>623800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>399200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>984700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>390300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>583200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1297600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2053100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2323000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1799700</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1161600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1141400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1145900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1549500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>925600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>913500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1326400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1487600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1213000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1250800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1524400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1289400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1861700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3334700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3086900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3162900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4465600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3500500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3026200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4226200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3716900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3676300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4506200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6272600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6361400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6372400</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3376400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3597100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2655900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1696400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3900200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3772100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1852600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3453500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3329000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2185000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3086500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4157200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5657500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E62" s="3">
         <v>101900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>91000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>111100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>84000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>80700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>70900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>70200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>209400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>351700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>307100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>421000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>494700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7110900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7119000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6361400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6742100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7599000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7008600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6232100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7326700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7791200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7765000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10362500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11431900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12993100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>875500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1041200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1630100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2910900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1077100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>765600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1220300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1304900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>760000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>650600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-239800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-768200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1816500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4676600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5195100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6025200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8363800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6507100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5905800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6317200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6598400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5682000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5801700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5570800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4874500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4960800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-594100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-686900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2213100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>120200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-641300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>427000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1436300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>245100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>157200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>589500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>133400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1702400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>980200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1058300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1019700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1207300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1250500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1193100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1206800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1244400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1522100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2049600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2232400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2503700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>706100</v>
+      </c>
+      <c r="E89" s="3">
         <v>326200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>877900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3778800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>916500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>693000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1313300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2843800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1150400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1976700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2283400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1741500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1189000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-821300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-874300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1170200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-614600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-555300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-987700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1135900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1479200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1449000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1066100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-611300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-893100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1441200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1009400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-785100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1038800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1095200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-630300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-939700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1472000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1325100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1011700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-472100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-814700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1436200</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E96" s="3">
         <v>200200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>311700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>102900</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>160900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>471600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>181700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-105600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-153400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-52000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-225600</v>
+      </c>
+      <c r="E100" s="3">
         <v>599500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>76600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3012000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>96200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>693400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1367100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-452000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>336100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1092800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1622400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-939600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-197600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-31000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>106000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-44400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-32700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-69300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-82800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-120400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>29400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-473500</v>
+      </c>
+      <c r="E102" s="3">
         <v>109500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-372700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>349700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>377300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1171400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>837000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>41100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-98300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>203600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-445600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AUOTY_YR_FIN.xlsx
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8960800</v>
+      </c>
+      <c r="E8" s="3">
         <v>8549300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8093400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8033400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13375900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9644900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8985200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10050100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11495600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10316900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11487800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14702600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14606000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12587900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7930500</v>
+      </c>
+      <c r="E9" s="3">
         <v>7810500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7942900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7982300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10100600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8834600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8969900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9130800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9438000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9235600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10217800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12955200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26827700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25900900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1030300</v>
+      </c>
+      <c r="E10" s="3">
         <v>738700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>150500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>51000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3275300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>810400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>919300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2057600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1081300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1270000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1747400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-12221700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-13312900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>508800</v>
+      </c>
+      <c r="E12" s="3">
         <v>489000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>431900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>418900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>471600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>366100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>327900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>311900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>332200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>284700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>283900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>329800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>299200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>329400</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -964,99 +980,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-318000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-210000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-60800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>17400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>60500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-42200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>42400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>30600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>383500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>82600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>140400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>800400</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>870400</v>
+      </c>
+      <c r="E15" s="3">
         <v>968700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1039700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1003200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1189700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1232500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1182900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1118200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1228000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19800</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8994400</v>
+      </c>
+      <c r="E17" s="3">
         <v>8807500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8810200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8813600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11099800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9570800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9669400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9831900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10176300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9960700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11312800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13986800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14455500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14139900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-258300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-716800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-780300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2276000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>74100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-684200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1319300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>356200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>175100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>715800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>150500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1552000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-76100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-33700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-161800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-118300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-116300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-139500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-150200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-117600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>79300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>149800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>149600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>368800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>220500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>868600</v>
+      </c>
+      <c r="E21" s="3">
         <v>786600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>356600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>384800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3584100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1422900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>638200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1486600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2664900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1677200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1820300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2908200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2752300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1176800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E22" s="3">
         <v>98100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>43900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>77100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>102000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>97700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>87000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>96700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>84900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>82600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>145700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>335600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>381200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-707700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-634900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2396200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>99200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-663400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>366400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1326900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>350700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>242300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>719700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>183700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1712700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E24" s="3">
         <v>71400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-115200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>106400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-37900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>143600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>87900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>116800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>47700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-89800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-592400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-682700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2289900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>103500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-722000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>355900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1364800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>207100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>154400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>602900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>136000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1750100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-93500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-594100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-686900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2213100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>120200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-641300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>427000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1436300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>245100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>157200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>589500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>133400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1702400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E32" s="3">
         <v>76100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>33700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>161800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>118300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>116300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>139500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>150200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>117600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-79300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-149800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-149600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-368800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-220500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-93500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-594100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-686900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2213100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>120200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-641300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>427000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1436300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>245100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>157200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>589500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>133400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1702400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-93500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-594100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-686900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2213100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>120200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-641300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>427000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1436300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>245100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>157200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>589500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>133400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1702400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,413 +2073,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1771100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2088100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2740700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2624000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2884700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3213400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2689300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2259500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3540100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2514000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2514700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2952400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2677000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2398600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>125600</v>
+        <v>16900</v>
       </c>
       <c r="E42" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F42" s="3">
         <v>68200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>360800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>34700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>126400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>101200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>374100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>238500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>181200</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1159900</v>
+      </c>
+      <c r="E43" s="3">
         <v>829800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>838300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>677100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2274200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1673800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1075400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1551300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1377400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1513900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1111600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2149100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1535600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1418200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1153200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1031500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>946600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>985100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1244500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>952300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>784200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>859500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>837800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>867700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1013600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1311900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1318900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1416400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>138900</v>
+        <v>297600</v>
       </c>
       <c r="E45" s="3">
+        <v>250200</v>
+      </c>
+      <c r="F45" s="3">
         <v>113100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>166900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>164800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>117200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>98400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>304700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>207700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>150200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>163600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>179600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>430500</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4398700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4213900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4706900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4562900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6929100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5991400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4786900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4869900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6073500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5120900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5164300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6685800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5949700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5845000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>711900</v>
+      </c>
+      <c r="E47" s="3">
         <v>932700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1045600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1132300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>990900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>715000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>452800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>433400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>335200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>257300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>463800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>535800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>493000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>511800</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5371400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5373100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5906500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6141000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6562300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7003800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7318800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7239000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7582200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6997600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6670900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8366700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9525100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10554300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>739700</v>
+      </c>
+      <c r="E49" s="3">
         <v>592400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>367800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>371000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>424200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>455700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>428200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>68500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>426400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>464700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>140000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>155500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>496700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>279300</v>
+      </c>
+      <c r="E52" s="3">
         <v>272500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>156400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>168500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>189000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>117500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>132400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>192800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>207600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>671000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>802900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>204900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>183100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>546100</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12165600</v>
+      </c>
+      <c r="E54" s="3">
         <v>11985000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12516200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12592100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15328900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14497200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13292200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13020300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14500500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13473300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13566700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15933200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16306400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17953800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1666700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1651500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1587500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1541900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2287700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1951100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1713500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1915100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1838900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1880100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1957900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2695200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2749000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1070300</v>
+      </c>
+      <c r="E58" s="3">
         <v>521600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>358000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>475100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>628400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>623800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>399200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>984700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>390300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>583200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1297600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2053100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2323000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1799700</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1196800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1161600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1141400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1145900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1549500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>925600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>913500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1326400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1487600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1213000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1250800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1524400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1289400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1861700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3933800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3334700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3086900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3162900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4465600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3500500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3026200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4226200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3716900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3676300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4506200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6272600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6361400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6372400</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2669600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3376400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3597100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2655900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1696400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3900200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3772100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1852600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3453500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3329000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2185000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3086500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4157200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5657500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E62" s="3">
         <v>74200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>101900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>91000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>111100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>84000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>80700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>70900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>70200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>209400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>351700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>307100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>421000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>494700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6948000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7110900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7119000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6361400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6742100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7599000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7008600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6232100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7326700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7791200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7765000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10362500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11431900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12993100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1110200</v>
+      </c>
+      <c r="E72" s="3">
         <v>875500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1041200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1630100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2910900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1077100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>765600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1220300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1304900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>760000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>650600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-239800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-768200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1816500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4840400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4676600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5195100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6025200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8363800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6507100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5905800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6317200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6598400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5682000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5801700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5570800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4874500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4960800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-93500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-594100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-686900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2213100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>120200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-641300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>427000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1436300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>245100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>157200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>589500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>133400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1702400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>980200</v>
+        <v>892900</v>
       </c>
       <c r="E83" s="3">
+        <v>985900</v>
+      </c>
+      <c r="F83" s="3">
         <v>1058300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1019700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1207300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1250500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1193100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1206800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1244400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1522100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2049600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2232400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2503700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>354400</v>
+      </c>
+      <c r="E89" s="3">
         <v>706100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>326200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>877900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3778800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>916500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>693000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1313300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2843800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1150400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1976700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2283400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1741500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-578800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-821300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-874300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1170200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-614600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-555300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-987700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1135900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1479200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1449000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1066100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-611300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-893100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1441200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-172700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1009400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-785100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1038800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1095200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-630300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-939700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1472000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1325100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1011700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-472100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-814700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1436200</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E96" s="3">
         <v>210500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>200200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>311700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>102900</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>160900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>471600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>181700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-105600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-153400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-52000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-610800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-225600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>599500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>76600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3012000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>96200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>693400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1367100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-452000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>336100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1092800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1622400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-939600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-197600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E101" s="3">
         <v>55400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-31000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>106000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-44400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-32700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-69300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-82800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-120400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>29400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>14700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-408600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-473500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>109500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-372700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>349700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>377300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1171400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>837000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>41100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-98300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>203600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-445600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
